--- a/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
+++ b/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\URIARTE 630\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E08477-6AB0-4BDC-B1C7-A2E93DC5F30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C31624-2C96-4E2F-AA00-66B006270BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,11 +20,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="70">
   <si>
     <t>UF</t>
   </si>
@@ -225,6 +230,15 @@
   </si>
   <si>
     <t>Liquidacion mes de ABRIL</t>
+  </si>
+  <si>
+    <t>AYSA  VTO 03/02/2026</t>
+  </si>
+  <si>
+    <t>AYSA VTO 07/04/2026</t>
+  </si>
+  <si>
+    <t>Subidos en Abr1l 2026</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1113,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1261,10 +1275,57 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1272,13 +1333,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1303,52 +1362,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1427,9 +1440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1467,9 +1480,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1502,9 +1515,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1537,9 +1567,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1716,43 +1763,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:G65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>27</v>
       </c>
@@ -1766,7 +1813,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1774,12 +1821,12 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
@@ -1791,7 +1838,7 @@
       </c>
       <c r="F11" s="113"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
         <v>32</v>
       </c>
@@ -1805,10 +1852,10 @@
         <v>20</v>
       </c>
       <c r="F12" s="31">
-        <v>-580115.74135200609</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-714046.60522400623</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="45" t="s">
         <v>33</v>
       </c>
@@ -1822,10 +1869,10 @@
       </c>
       <c r="F13" s="98">
         <f>'prorrateo '!F10</f>
-        <v>760627.49112799985</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
         <v>46</v>
       </c>
@@ -1838,269 +1885,285 @@
         <v>59</v>
       </c>
       <c r="F14" s="99">
-        <f>-C24</f>
-        <v>-585331.17499999993</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-C25</f>
+        <v>-627830.20499999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
         <v>51</v>
       </c>
       <c r="B15" s="106"/>
-      <c r="C15" s="110">
+      <c r="C15" s="43">
         <v>162057</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="97"/>
       <c r="F15" s="100"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="B16" s="107"/>
-      <c r="C16" s="148">
-        <v>16776.5</v>
+      <c r="C16" s="101">
+        <f>16422.66</f>
+        <v>16422.66</v>
       </c>
       <c r="E16" s="97"/>
       <c r="F16" s="100"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="148">
-        <v>52091.69</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="B17" s="107"/>
+      <c r="C17" s="101">
+        <f>16742.23+2154.33</f>
+        <v>18896.559999999998</v>
+      </c>
       <c r="E17" s="97"/>
       <c r="F17" s="100"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="108"/>
-      <c r="C18" s="148">
-        <v>258515.27</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B18" s="106"/>
+      <c r="C18" s="101">
+        <v>76048</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="97"/>
       <c r="F18" s="100"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="106"/>
+        <v>29</v>
+      </c>
+      <c r="B19" s="108"/>
       <c r="C19" s="101">
-        <v>0</v>
+        <v>258515.27</v>
       </c>
       <c r="E19" s="97"/>
       <c r="F19" s="100"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="106"/>
+      <c r="C20" s="101">
+        <v>0</v>
+      </c>
+      <c r="E20" s="97"/>
+      <c r="F20" s="100"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="109"/>
-      <c r="C20" s="102">
-        <f>SUM(C12:C19)</f>
-        <v>585331.17499999993</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="32" t="s">
+      <c r="B21" s="109"/>
+      <c r="C21" s="102">
+        <f>SUM(C12:C20)</f>
+        <v>627830.20499999996</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="33">
-        <f>SUM(F12:F18)</f>
-        <v>-404819.42522400618</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="48" t="s">
+      <c r="F21" s="33">
+        <f>SUM(F12:F19)</f>
+        <v>-711876.81022400619</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
       <c r="B22" s="106"/>
-      <c r="C22" s="110"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="44">
-        <f>SUM(C21:C22)</f>
+      <c r="B24" s="22"/>
+      <c r="C24" s="44">
+        <f>SUM(C22:C23)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
+      <c r="D24" s="4"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="73">
-        <f>+C23+C20</f>
-        <v>585331.17499999993</v>
-      </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="73">
+        <f>+C24+C21</f>
+        <v>627830.20499999996</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="74"/>
-    </row>
-    <row r="26" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="B26" s="42"/>
+      <c r="C26" s="74"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="75"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="75"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="29"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="76">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="77"/>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="114"/>
-      <c r="B31" s="114"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="29"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="76">
+    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="76">
         <v>0</v>
       </c>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="77"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="114"/>
+      <c r="B32" s="114"/>
+      <c r="C32" s="76"/>
+    </row>
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="29"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="76">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="50">
-        <f>SUM(C28:C32)</f>
+      <c r="B34" s="37"/>
+      <c r="C34" s="50">
+        <f>SUM(C29:C33)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C34" s="76"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="76"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="78">
-        <f>C34+C24</f>
-        <v>585331.17499999993</v>
-      </c>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
+      <c r="C36" s="78">
+        <f>C35+C25</f>
+        <v>627830.20499999996</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="50">
-        <f>+C24+C33</f>
-        <v>585331.17499999993</v>
-      </c>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="37"/>
+      <c r="C37" s="50">
+        <f>+C25+C34</f>
+        <v>627830.20499999996</v>
+      </c>
+      <c r="E37" s="10"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="10"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="13"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="12"/>
       <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="13"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2118,53 +2181,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="11" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="145" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
       <c r="D1" s="83"/>
       <c r="E1" s="84" t="s">
         <v>26</v>
       </c>
       <c r="F1" s="83"/>
-      <c r="G1" s="125" t="s">
+      <c r="G1" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="127"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="142"/>
       <c r="K1" s="104"/>
-      <c r="L1" s="128">
+      <c r="L1" s="143">
         <f>O1</f>
         <v>1000000</v>
       </c>
-      <c r="M1" s="129"/>
+      <c r="M1" s="144"/>
       <c r="O1" s="14">
         <v>1000000</v>
       </c>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="85" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 15/05</v>
@@ -2186,38 +2249,38 @@
         <v>413723.43999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="126" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="124" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="142" t="s">
+      <c r="E3" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="142" t="s">
+      <c r="F3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="142" t="s">
+      <c r="G3" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="142" t="s">
+      <c r="H3" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="146" t="s">
+      <c r="I3" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="146" t="s">
+      <c r="J3" s="128" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="142" t="s">
+      <c r="K3" s="124" t="s">
         <v>63</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -2227,20 +2290,20 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="145"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="127"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="143"/>
+      <c r="C4" s="125"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="143"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="125"/>
       <c r="L4" s="80" t="str">
         <f>A2</f>
         <v>Vto. 15/05</v>
@@ -2249,7 +2312,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="86">
         <v>1</v>
       </c>
@@ -2263,11 +2326,11 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>109688.35222799999</v>
+        <v>210000</v>
       </c>
       <c r="F5" s="43">
         <f>E5</f>
-        <v>109688.35222799999</v>
+        <v>210000</v>
       </c>
       <c r="G5" s="81">
         <f>E5-F5</f>
@@ -2295,7 +2358,7 @@
         <v>218400</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="86">
         <v>2</v>
       </c>
@@ -2309,18 +2372,18 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>451138.38309959357</v>
+        <v>172074.00727995942</v>
       </c>
       <c r="F6" s="43">
-        <v>440000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="81">
         <f t="shared" ref="G6:G9" si="1">E6-F6</f>
-        <v>11138.383099593571</v>
+        <v>172074.00727995942</v>
       </c>
       <c r="H6" s="82">
         <f t="shared" ref="H6:H9" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>935.62418036586007</v>
+        <v>14454.216611516593</v>
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
@@ -2333,14 +2396,14 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>172074.00727995942</v>
+        <v>346528.22389147605</v>
       </c>
       <c r="M6" s="88">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>178956.96757115779</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>360389.3528471351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="86">
         <v>3</v>
       </c>
@@ -2352,16 +2415,18 @@
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="23">
-        <v>151928.21224797762</v>
-      </c>
-      <c r="F7" s="43"/>
+        <v>374690.18207680772</v>
+      </c>
+      <c r="F7" s="43">
+        <v>0</v>
+      </c>
       <c r="G7" s="81">
         <f t="shared" si="1"/>
-        <v>151928.21224797762</v>
+        <v>374690.18207680772</v>
       </c>
       <c r="H7" s="82">
         <f t="shared" si="2"/>
-        <v>12761.969828830121</v>
+        <v>31473.975294451851</v>
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
@@ -2373,14 +2438,14 @@
       <c r="K7" s="111"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
-        <v>374690.18207680772</v>
+        <v>616164.15737125953</v>
       </c>
       <c r="M7" s="88">
         <f t="shared" si="3"/>
-        <v>389677.78935988003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>640810.72366610996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="86">
         <v>4</v>
       </c>
@@ -2392,11 +2457,11 @@
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="23">
-        <v>105469.56945</v>
+        <v>210000</v>
       </c>
       <c r="F8" s="43">
         <f>E8</f>
-        <v>105469.56945</v>
+        <v>210000</v>
       </c>
       <c r="G8" s="81">
         <f t="shared" si="1"/>
@@ -2423,7 +2488,7 @@
         <v>218400</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="86">
         <v>5</v>
       </c>
@@ -2435,11 +2500,11 @@
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="23">
-        <v>105469.56945</v>
+        <v>210000</v>
       </c>
       <c r="F9" s="43">
         <f>E9</f>
-        <v>105469.56945</v>
+        <v>210000</v>
       </c>
       <c r="G9" s="81">
         <f t="shared" si="1"/>
@@ -2466,7 +2531,7 @@
         <v>218400</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="89" t="s">
         <v>7</v>
       </c>
@@ -2481,19 +2546,19 @@
       </c>
       <c r="E10" s="93">
         <f>SUM(E5:E9)</f>
-        <v>923694.08647557104</v>
+        <v>1176764.1893567671</v>
       </c>
       <c r="F10" s="93">
         <f>SUM(F5:F9)</f>
-        <v>760627.49112799985</v>
+        <v>630000</v>
       </c>
       <c r="G10" s="93">
         <f t="shared" si="4"/>
-        <v>11138.383099593571</v>
+        <v>172074.00727995942</v>
       </c>
       <c r="H10" s="93">
         <f t="shared" si="4"/>
-        <v>935.62418036586007</v>
+        <v>14454.216611516593</v>
       </c>
       <c r="I10" s="94">
         <f>SUM(I5:I9)</f>
@@ -2506,55 +2571,55 @@
       <c r="K10" s="94"/>
       <c r="L10" s="93">
         <f>SUM(L5:L9)</f>
-        <v>1176764.1893567671</v>
+        <v>1592692.3812627355</v>
       </c>
       <c r="M10" s="95">
         <f>SUM(M5:M9)</f>
-        <v>1223834.7569310379</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1656400.0765132452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="147"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="147"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="147"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="117" t="s">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
       <c r="I14" s="54"/>
       <c r="J14" s="55"/>
       <c r="K14" s="59"/>
       <c r="L14" s="59"/>
     </row>
-    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="119" t="s">
+    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
       <c r="I15" s="56"/>
       <c r="J15" s="57"/>
       <c r="K15" s="59"/>
@@ -2566,7 +2631,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="54"/>
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
@@ -2586,7 +2651,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" s="56" t="s">
         <v>38</v>
       </c>
@@ -2608,7 +2673,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" s="60"/>
       <c r="D18" s="61"/>
       <c r="E18" s="61"/>
@@ -2626,21 +2691,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="115" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
       <c r="I19" s="56"/>
       <c r="J19" s="57"/>
       <c r="K19" s="59"/>
       <c r="L19" s="59"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" s="56"/>
       <c r="D20" s="59"/>
       <c r="E20" s="59"/>
@@ -2658,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" s="56" t="s">
         <v>40</v>
       </c>
@@ -2672,14 +2737,14 @@
         <v>41</v>
       </c>
       <c r="H21" s="62"/>
-      <c r="I21" s="120" t="s">
+      <c r="I21" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="121"/>
+      <c r="J21" s="133"/>
       <c r="K21" s="71"/>
       <c r="L21" s="71"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" s="56" t="s">
         <v>43</v>
       </c>
@@ -2698,19 +2763,19 @@
       <c r="K22" s="59"/>
       <c r="L22" s="59"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="56"/>
       <c r="D23" s="59"/>
       <c r="E23" s="59"/>
       <c r="F23" s="59"/>
       <c r="G23" s="59"/>
       <c r="H23" s="59"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="121"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="133"/>
       <c r="K23" s="71"/>
       <c r="L23" s="71"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" s="69" t="s">
         <v>46</v>
       </c>
@@ -2727,7 +2792,7 @@
       <c r="K24" s="59"/>
       <c r="L24" s="59"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" s="70" t="s">
         <v>30</v>
       </c>
@@ -2744,7 +2809,7 @@
       <c r="K25" s="59"/>
       <c r="L25" s="59"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" s="70" t="s">
         <v>28</v>
       </c>
@@ -2761,7 +2826,7 @@
       <c r="K26" s="59"/>
       <c r="L26" s="59"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" s="70" t="s">
         <v>31</v>
       </c>
@@ -2778,7 +2843,7 @@
       <c r="K27" s="59"/>
       <c r="L27" s="59"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="70" t="s">
         <v>29</v>
       </c>
@@ -2795,7 +2860,7 @@
       <c r="K28" s="59"/>
       <c r="L28" s="59"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="D29" s="59"/>
       <c r="E29" s="59"/>
       <c r="F29" s="59"/>
@@ -2806,7 +2871,7 @@
       <c r="K29" s="59"/>
       <c r="L29" s="59"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C30" s="70" t="s">
         <v>34</v>
       </c>
@@ -2823,7 +2888,7 @@
       <c r="K30" s="59"/>
       <c r="L30" s="59"/>
     </row>
-    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C31" s="56"/>
       <c r="D31" s="59"/>
       <c r="E31" s="59"/>
@@ -2835,14 +2900,14 @@
       <c r="K31" s="59"/>
       <c r="L31" s="59"/>
     </row>
-    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="123" t="s">
+    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
       <c r="H32" s="105">
         <f>SUM(H24:H31)</f>
         <v>245366.38250000001</v>
@@ -2852,38 +2917,38 @@
       <c r="K32" s="59"/>
       <c r="L32" s="59"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="117" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
       <c r="I36" s="54"/>
       <c r="J36" s="55"/>
       <c r="K36" s="59"/>
       <c r="L36" s="59"/>
     </row>
-    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="119" t="s">
+    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="135"/>
       <c r="I37" s="56"/>
       <c r="J37" s="57"/>
       <c r="K37" s="59"/>
       <c r="L37" s="59"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="54"/>
       <c r="D38" s="58"/>
       <c r="E38" s="58"/>
@@ -2897,7 +2962,7 @@
       <c r="K38" s="59"/>
       <c r="L38" s="59"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="56" t="s">
         <v>38</v>
       </c>
@@ -2914,7 +2979,7 @@
       <c r="K39" s="59"/>
       <c r="L39" s="59"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="60"/>
       <c r="D40" s="61"/>
       <c r="E40" s="61"/>
@@ -2926,21 +2991,21 @@
       <c r="K40" s="59"/>
       <c r="L40" s="59"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="115" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="116"/>
-      <c r="E41" s="116"/>
-      <c r="F41" s="116"/>
-      <c r="G41" s="116"/>
-      <c r="H41" s="116"/>
+      <c r="D41" s="138"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="138"/>
       <c r="I41" s="56"/>
       <c r="J41" s="57"/>
       <c r="K41" s="59"/>
       <c r="L41" s="59"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="56"/>
       <c r="D42" s="59"/>
       <c r="E42" s="59"/>
@@ -2952,7 +3017,7 @@
       <c r="K42" s="59"/>
       <c r="L42" s="59"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="56" t="s">
         <v>40</v>
       </c>
@@ -2966,14 +3031,14 @@
         <v>41</v>
       </c>
       <c r="H43" s="62"/>
-      <c r="I43" s="120" t="s">
+      <c r="I43" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J43" s="121"/>
+      <c r="J43" s="133"/>
       <c r="K43" s="71"/>
       <c r="L43" s="71"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="56" t="s">
         <v>43</v>
       </c>
@@ -2992,19 +3057,19 @@
       <c r="K44" s="59"/>
       <c r="L44" s="59"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="56"/>
       <c r="D45" s="59"/>
       <c r="E45" s="59"/>
       <c r="F45" s="59"/>
       <c r="G45" s="59"/>
       <c r="H45" s="59"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="121"/>
+      <c r="I45" s="139"/>
+      <c r="J45" s="133"/>
       <c r="K45" s="71"/>
       <c r="L45" s="71"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="56" t="s">
         <v>46</v>
       </c>
@@ -3021,7 +3086,7 @@
       <c r="K46" s="59"/>
       <c r="L46" s="59"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="56"/>
       <c r="D47" s="59"/>
       <c r="E47" s="59"/>
@@ -3033,7 +3098,7 @@
       <c r="K47" s="59"/>
       <c r="L47" s="59"/>
     </row>
-    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="56"/>
       <c r="D48" s="59"/>
       <c r="E48" s="59"/>
@@ -3045,54 +3110,54 @@
       <c r="K48" s="59"/>
       <c r="L48" s="59"/>
     </row>
-    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="123" t="s">
+    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
+      <c r="D49" s="131"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="131"/>
       <c r="H49" s="105">
         <f>M6</f>
-        <v>178956.96757115779</v>
+        <v>360389.3528471351</v>
       </c>
       <c r="I49" s="66"/>
       <c r="J49" s="67"/>
       <c r="K49" s="59"/>
       <c r="L49" s="59"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="117" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
+      <c r="D52" s="135"/>
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
       <c r="I52" s="54"/>
       <c r="J52" s="55"/>
       <c r="K52" s="59"/>
       <c r="L52" s="59"/>
     </row>
-    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="119" t="s">
+    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
+      <c r="D53" s="135"/>
+      <c r="E53" s="135"/>
+      <c r="F53" s="135"/>
+      <c r="G53" s="135"/>
+      <c r="H53" s="135"/>
       <c r="I53" s="56"/>
       <c r="J53" s="57"/>
       <c r="K53" s="59"/>
       <c r="L53" s="59"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="54"/>
       <c r="D54" s="58"/>
       <c r="E54" s="58"/>
@@ -3106,7 +3171,7 @@
       <c r="K54" s="59"/>
       <c r="L54" s="59"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="56" t="s">
         <v>38</v>
       </c>
@@ -3123,7 +3188,7 @@
       <c r="K55" s="59"/>
       <c r="L55" s="59"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="60"/>
       <c r="D56" s="61"/>
       <c r="E56" s="61"/>
@@ -3135,21 +3200,21 @@
       <c r="K56" s="59"/>
       <c r="L56" s="59"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="115" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="116"/>
-      <c r="E57" s="116"/>
-      <c r="F57" s="116"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="116"/>
+      <c r="D57" s="138"/>
+      <c r="E57" s="138"/>
+      <c r="F57" s="138"/>
+      <c r="G57" s="138"/>
+      <c r="H57" s="138"/>
       <c r="I57" s="56"/>
       <c r="J57" s="57"/>
       <c r="K57" s="59"/>
       <c r="L57" s="59"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="56"/>
       <c r="D58" s="59"/>
       <c r="E58" s="59"/>
@@ -3161,7 +3226,7 @@
       <c r="K58" s="59"/>
       <c r="L58" s="59"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="56" t="s">
         <v>40</v>
       </c>
@@ -3175,14 +3240,14 @@
         <v>41</v>
       </c>
       <c r="H59" s="62"/>
-      <c r="I59" s="120" t="s">
+      <c r="I59" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="121"/>
+      <c r="J59" s="133"/>
       <c r="K59" s="71"/>
       <c r="L59" s="71"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="56" t="s">
         <v>43</v>
       </c>
@@ -3201,19 +3266,19 @@
       <c r="K60" s="59"/>
       <c r="L60" s="59"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="56"/>
       <c r="D61" s="59"/>
       <c r="E61" s="59"/>
       <c r="F61" s="59"/>
       <c r="G61" s="59"/>
       <c r="H61" s="59"/>
-      <c r="I61" s="122"/>
-      <c r="J61" s="121"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="133"/>
       <c r="K61" s="71"/>
       <c r="L61" s="71"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="56" t="s">
         <v>46</v>
       </c>
@@ -3230,7 +3295,7 @@
       <c r="K62" s="59"/>
       <c r="L62" s="59"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="70" t="s">
         <v>30</v>
       </c>
@@ -3247,7 +3312,7 @@
       <c r="K63" s="59"/>
       <c r="L63" s="59"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="70" t="s">
         <v>28</v>
       </c>
@@ -3264,7 +3329,7 @@
       <c r="K64" s="59"/>
       <c r="L64" s="59"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="70" t="s">
         <v>31</v>
       </c>
@@ -3281,7 +3346,7 @@
       <c r="K65" s="59"/>
       <c r="L65" s="59"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="70" t="s">
         <v>29</v>
       </c>
@@ -3298,7 +3363,7 @@
       <c r="K66" s="59"/>
       <c r="L66" s="59"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D67" s="59"/>
       <c r="E67" s="59"/>
       <c r="F67" s="59"/>
@@ -3309,7 +3374,7 @@
       <c r="K67" s="59"/>
       <c r="L67" s="59"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="70" t="s">
         <v>34</v>
       </c>
@@ -3326,7 +3391,7 @@
       <c r="K68" s="59"/>
       <c r="L68" s="59"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="56"/>
       <c r="D69" s="59"/>
       <c r="E69" s="59"/>
@@ -3338,7 +3403,7 @@
       <c r="K69" s="59"/>
       <c r="L69" s="59"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" s="56"/>
       <c r="D70" s="59"/>
       <c r="E70" s="59"/>
@@ -3350,7 +3415,7 @@
       <c r="K70" s="59"/>
       <c r="L70" s="59"/>
     </row>
-    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" s="56"/>
       <c r="D71" s="59"/>
       <c r="E71" s="59"/>
@@ -3362,14 +3427,14 @@
       <c r="K71" s="59"/>
       <c r="L71" s="59"/>
     </row>
-    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="123" t="s">
+    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="124"/>
-      <c r="G72" s="124"/>
+      <c r="D72" s="131"/>
+      <c r="E72" s="131"/>
+      <c r="F72" s="131"/>
+      <c r="G72" s="131"/>
       <c r="H72" s="105">
         <f>SUM(H62:H71)</f>
         <v>245366.38250000001</v>
@@ -3379,38 +3444,38 @@
       <c r="K72" s="59"/>
       <c r="L72" s="59"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="117" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="D76" s="118"/>
-      <c r="E76" s="118"/>
-      <c r="F76" s="118"/>
-      <c r="G76" s="118"/>
-      <c r="H76" s="118"/>
+      <c r="D76" s="135"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="135"/>
+      <c r="G76" s="135"/>
+      <c r="H76" s="135"/>
       <c r="I76" s="54"/>
       <c r="J76" s="55"/>
       <c r="K76" s="59"/>
       <c r="L76" s="59"/>
     </row>
-    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="119" t="s">
+    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="118"/>
-      <c r="G77" s="118"/>
-      <c r="H77" s="118"/>
+      <c r="D77" s="135"/>
+      <c r="E77" s="135"/>
+      <c r="F77" s="135"/>
+      <c r="G77" s="135"/>
+      <c r="H77" s="135"/>
       <c r="I77" s="56"/>
       <c r="J77" s="57"/>
       <c r="K77" s="59"/>
       <c r="L77" s="59"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="54"/>
       <c r="D78" s="58"/>
       <c r="E78" s="58"/>
@@ -3424,7 +3489,7 @@
       <c r="K78" s="59"/>
       <c r="L78" s="59"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="56" t="s">
         <v>38</v>
       </c>
@@ -3441,7 +3506,7 @@
       <c r="K79" s="59"/>
       <c r="L79" s="59"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="60"/>
       <c r="D80" s="61"/>
       <c r="E80" s="61"/>
@@ -3453,21 +3518,21 @@
       <c r="K80" s="59"/>
       <c r="L80" s="59"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="115" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="D81" s="116"/>
-      <c r="E81" s="116"/>
-      <c r="F81" s="116"/>
-      <c r="G81" s="116"/>
-      <c r="H81" s="116"/>
+      <c r="D81" s="138"/>
+      <c r="E81" s="138"/>
+      <c r="F81" s="138"/>
+      <c r="G81" s="138"/>
+      <c r="H81" s="138"/>
       <c r="I81" s="56"/>
       <c r="J81" s="57"/>
       <c r="K81" s="59"/>
       <c r="L81" s="59"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="56"/>
       <c r="D82" s="59"/>
       <c r="E82" s="59"/>
@@ -3479,7 +3544,7 @@
       <c r="K82" s="59"/>
       <c r="L82" s="59"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="56" t="s">
         <v>40</v>
       </c>
@@ -3493,14 +3558,14 @@
         <v>41</v>
       </c>
       <c r="H83" s="62"/>
-      <c r="I83" s="120" t="s">
+      <c r="I83" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J83" s="121"/>
+      <c r="J83" s="133"/>
       <c r="K83" s="71"/>
       <c r="L83" s="71"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="56" t="s">
         <v>43</v>
       </c>
@@ -3519,19 +3584,19 @@
       <c r="K84" s="59"/>
       <c r="L84" s="59"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="56"/>
       <c r="D85" s="59"/>
       <c r="E85" s="59"/>
       <c r="F85" s="59"/>
       <c r="G85" s="59"/>
       <c r="H85" s="59"/>
-      <c r="I85" s="122"/>
-      <c r="J85" s="121"/>
+      <c r="I85" s="139"/>
+      <c r="J85" s="133"/>
       <c r="K85" s="71"/>
       <c r="L85" s="71"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="56" t="s">
         <v>46</v>
       </c>
@@ -3548,7 +3613,7 @@
       <c r="K86" s="59"/>
       <c r="L86" s="59"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="70" t="s">
         <v>30</v>
       </c>
@@ -3565,7 +3630,7 @@
       <c r="K87" s="59"/>
       <c r="L87" s="59"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="70" t="s">
         <v>28</v>
       </c>
@@ -3582,7 +3647,7 @@
       <c r="K88" s="59"/>
       <c r="L88" s="59"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="70" t="s">
         <v>31</v>
       </c>
@@ -3599,7 +3664,7 @@
       <c r="K89" s="59"/>
       <c r="L89" s="59"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="70" t="s">
         <v>29</v>
       </c>
@@ -3616,7 +3681,7 @@
       <c r="K90" s="59"/>
       <c r="L90" s="59"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D91" s="59"/>
       <c r="E91" s="59"/>
       <c r="F91" s="59"/>
@@ -3627,7 +3692,7 @@
       <c r="K91" s="59"/>
       <c r="L91" s="59"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="70" t="s">
         <v>34</v>
       </c>
@@ -3644,7 +3709,7 @@
       <c r="K92" s="59"/>
       <c r="L92" s="59"/>
     </row>
-    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D93" s="59"/>
       <c r="E93" s="59"/>
       <c r="F93" s="59"/>
@@ -3655,14 +3720,14 @@
       <c r="K93" s="59"/>
       <c r="L93" s="59"/>
     </row>
-    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="123" t="s">
+    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="124"/>
-      <c r="E94" s="124"/>
-      <c r="F94" s="124"/>
-      <c r="G94" s="124"/>
+      <c r="D94" s="131"/>
+      <c r="E94" s="131"/>
+      <c r="F94" s="131"/>
+      <c r="G94" s="131"/>
       <c r="H94" s="105">
         <f>SUM(H86:H93)</f>
         <v>245366.38250000001</v>
@@ -3672,38 +3737,38 @@
       <c r="K94" s="59"/>
       <c r="L94" s="59"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="117" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="D98" s="118"/>
-      <c r="E98" s="118"/>
-      <c r="F98" s="118"/>
-      <c r="G98" s="118"/>
-      <c r="H98" s="118"/>
+      <c r="D98" s="135"/>
+      <c r="E98" s="135"/>
+      <c r="F98" s="135"/>
+      <c r="G98" s="135"/>
+      <c r="H98" s="135"/>
       <c r="I98" s="54"/>
       <c r="J98" s="55"/>
       <c r="K98" s="59"/>
       <c r="L98" s="59"/>
     </row>
-    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="119" t="s">
+    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="118"/>
-      <c r="E99" s="118"/>
-      <c r="F99" s="118"/>
-      <c r="G99" s="118"/>
-      <c r="H99" s="118"/>
+      <c r="D99" s="135"/>
+      <c r="E99" s="135"/>
+      <c r="F99" s="135"/>
+      <c r="G99" s="135"/>
+      <c r="H99" s="135"/>
       <c r="I99" s="56"/>
       <c r="J99" s="57"/>
       <c r="K99" s="59"/>
       <c r="L99" s="59"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="54"/>
       <c r="D100" s="58"/>
       <c r="E100" s="58"/>
@@ -3717,7 +3782,7 @@
       <c r="K100" s="59"/>
       <c r="L100" s="59"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="56" t="s">
         <v>38</v>
       </c>
@@ -3734,7 +3799,7 @@
       <c r="K101" s="59"/>
       <c r="L101" s="59"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="60"/>
       <c r="D102" s="61"/>
       <c r="E102" s="61"/>
@@ -3746,21 +3811,21 @@
       <c r="K102" s="59"/>
       <c r="L102" s="59"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="115" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="D103" s="116"/>
-      <c r="E103" s="116"/>
-      <c r="F103" s="116"/>
-      <c r="G103" s="116"/>
-      <c r="H103" s="116"/>
+      <c r="D103" s="138"/>
+      <c r="E103" s="138"/>
+      <c r="F103" s="138"/>
+      <c r="G103" s="138"/>
+      <c r="H103" s="138"/>
       <c r="I103" s="56"/>
       <c r="J103" s="57"/>
       <c r="K103" s="59"/>
       <c r="L103" s="59"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="56"/>
       <c r="D104" s="59"/>
       <c r="E104" s="59"/>
@@ -3772,7 +3837,7 @@
       <c r="K104" s="59"/>
       <c r="L104" s="59"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="56" t="s">
         <v>40</v>
       </c>
@@ -3786,14 +3851,14 @@
         <v>41</v>
       </c>
       <c r="H105" s="62"/>
-      <c r="I105" s="120" t="s">
+      <c r="I105" s="132" t="s">
         <v>42</v>
       </c>
-      <c r="J105" s="121"/>
+      <c r="J105" s="133"/>
       <c r="K105" s="71"/>
       <c r="L105" s="71"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="56" t="s">
         <v>43</v>
       </c>
@@ -3811,19 +3876,19 @@
       <c r="K106" s="59"/>
       <c r="L106" s="59"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="56"/>
       <c r="D107" s="59"/>
       <c r="E107" s="59"/>
       <c r="F107" s="59"/>
       <c r="G107" s="59"/>
       <c r="H107" s="59"/>
-      <c r="I107" s="122"/>
-      <c r="J107" s="121"/>
+      <c r="I107" s="139"/>
+      <c r="J107" s="133"/>
       <c r="K107" s="71"/>
       <c r="L107" s="71"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="56" t="s">
         <v>46</v>
       </c>
@@ -3840,7 +3905,7 @@
       <c r="K108" s="59"/>
       <c r="L108" s="59"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="70" t="s">
         <v>30</v>
       </c>
@@ -3857,7 +3922,7 @@
       <c r="K109" s="59"/>
       <c r="L109" s="59"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="70" t="s">
         <v>28</v>
       </c>
@@ -3874,7 +3939,7 @@
       <c r="K110" s="59"/>
       <c r="L110" s="59"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="70" t="s">
         <v>31</v>
       </c>
@@ -3891,7 +3956,7 @@
       <c r="K111" s="59"/>
       <c r="L111" s="59"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="70" t="s">
         <v>29</v>
       </c>
@@ -3908,7 +3973,7 @@
       <c r="K112" s="59"/>
       <c r="L112" s="59"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D113" s="59"/>
       <c r="E113" s="59"/>
       <c r="F113" s="59"/>
@@ -3919,7 +3984,7 @@
       <c r="K113" s="59"/>
       <c r="L113" s="59"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="70" t="s">
         <v>34</v>
       </c>
@@ -3936,7 +4001,7 @@
       <c r="K114" s="59"/>
       <c r="L114" s="59"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D115" s="59"/>
       <c r="E115" s="59"/>
       <c r="F115" s="59"/>
@@ -3947,14 +4012,14 @@
       <c r="K115" s="59"/>
       <c r="L115" s="59"/>
     </row>
-    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="123" t="s">
+    <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D116" s="124"/>
-      <c r="E116" s="124"/>
-      <c r="F116" s="124"/>
-      <c r="G116" s="124"/>
+      <c r="D116" s="131"/>
+      <c r="E116" s="131"/>
+      <c r="F116" s="131"/>
+      <c r="G116" s="131"/>
       <c r="H116" s="105">
         <f>SUM(H108:H115)</f>
         <v>245366.38250000001</v>
@@ -3964,57 +4029,85 @@
       <c r="K116" s="59"/>
       <c r="L116" s="59"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="133" t="s">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="B119" s="134"/>
-      <c r="C119" s="134"/>
-      <c r="D119" s="134"/>
-      <c r="E119" s="134"/>
-      <c r="F119" s="134"/>
-      <c r="G119" s="134"/>
-      <c r="H119" s="134"/>
-      <c r="I119" s="134"/>
-      <c r="J119" s="134"/>
-      <c r="K119" s="134"/>
-      <c r="L119" s="134"/>
-      <c r="M119" s="135"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="136"/>
-      <c r="B120" s="137"/>
-      <c r="C120" s="137"/>
-      <c r="D120" s="137"/>
-      <c r="E120" s="137"/>
-      <c r="F120" s="137"/>
-      <c r="G120" s="137"/>
-      <c r="H120" s="137"/>
-      <c r="I120" s="137"/>
-      <c r="J120" s="137"/>
-      <c r="K120" s="137"/>
-      <c r="L120" s="137"/>
-      <c r="M120" s="138"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="139"/>
-      <c r="B121" s="140"/>
-      <c r="C121" s="140"/>
-      <c r="D121" s="140"/>
-      <c r="E121" s="140"/>
-      <c r="F121" s="140"/>
-      <c r="G121" s="140"/>
-      <c r="H121" s="140"/>
-      <c r="I121" s="140"/>
-      <c r="J121" s="140"/>
-      <c r="K121" s="140"/>
-      <c r="L121" s="140"/>
-      <c r="M121" s="141"/>
+      <c r="B119" s="116"/>
+      <c r="C119" s="116"/>
+      <c r="D119" s="116"/>
+      <c r="E119" s="116"/>
+      <c r="F119" s="116"/>
+      <c r="G119" s="116"/>
+      <c r="H119" s="116"/>
+      <c r="I119" s="116"/>
+      <c r="J119" s="116"/>
+      <c r="K119" s="116"/>
+      <c r="L119" s="116"/>
+      <c r="M119" s="117"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="118"/>
+      <c r="B120" s="119"/>
+      <c r="C120" s="119"/>
+      <c r="D120" s="119"/>
+      <c r="E120" s="119"/>
+      <c r="F120" s="119"/>
+      <c r="G120" s="119"/>
+      <c r="H120" s="119"/>
+      <c r="I120" s="119"/>
+      <c r="J120" s="119"/>
+      <c r="K120" s="119"/>
+      <c r="L120" s="119"/>
+      <c r="M120" s="120"/>
+    </row>
+    <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="121"/>
+      <c r="B121" s="122"/>
+      <c r="C121" s="122"/>
+      <c r="D121" s="122"/>
+      <c r="E121" s="122"/>
+      <c r="F121" s="122"/>
+      <c r="G121" s="122"/>
+      <c r="H121" s="122"/>
+      <c r="I121" s="122"/>
+      <c r="J121" s="122"/>
+      <c r="K121" s="122"/>
+      <c r="L121" s="122"/>
+      <c r="M121" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I45:J45"/>
     <mergeCell ref="A119:M121"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C4"/>
@@ -4031,34 +4124,6 @@
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="I107:J107"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
+++ b/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C31624-2C96-4E2F-AA00-66B006270BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E106F5-83E8-48E8-BB86-5FBCB927A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,8 @@
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -239,18 +240,25 @@
   </si>
   <si>
     <t>Subidos en Abr1l 2026</t>
+  </si>
+  <si>
+    <t>Recuperacion de intereses por pago fuera de termino a administracion - Desde enero 25 a dia de la fecha - Debido a que la caja inicial pertenece a la administracion</t>
+  </si>
+  <si>
+    <t>Prevision ordinaria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="172" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -430,7 +438,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -465,17 +473,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -581,17 +578,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -635,17 +621,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1107,18 +1082,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1138,79 +1161,65 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1221,43 +1230,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1266,16 +1274,67 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1287,81 +1346,47 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="1" fillId="6" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1763,7 +1788,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G65"/>
+  <dimension ref="A2:G59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1804,12 +1829,12 @@
         <v>27</v>
       </c>
       <c r="B7" s="17"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="46" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1833,167 +1858,171 @@
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="112" t="s">
+      <c r="E11" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="113"/>
+      <c r="F11" s="104"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="106"/>
-      <c r="C12" s="101">
+      <c r="B12" s="97"/>
+      <c r="C12" s="92">
         <f>86199+86199*6%</f>
         <v>91370.94</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>-714046.60522400623</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="101">
+      <c r="B13" s="97"/>
+      <c r="C13" s="92">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="97" t="s">
+      <c r="E13" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="98">
+      <c r="F13" s="90">
         <f>'prorrateo '!F10</f>
         <v>630000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="43">
+      <c r="B14" s="97"/>
+      <c r="C14" s="38">
         <v>0</v>
       </c>
       <c r="D14" s="24"/>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="99">
+      <c r="F14" s="144">
         <f>-C25</f>
         <v>-627830.20499999996</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="106"/>
-      <c r="C15" s="43">
+      <c r="B15" s="97"/>
+      <c r="C15" s="38">
         <v>162057</v>
       </c>
       <c r="D15" s="24"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="100"/>
+      <c r="E15" s="138" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="141">
+        <v>-119176.45</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="107"/>
-      <c r="C16" s="101">
+      <c r="B16" s="98"/>
+      <c r="C16" s="92">
         <f>16422.66</f>
         <v>16422.66</v>
       </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="100"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="142"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="107"/>
-      <c r="C17" s="101">
+      <c r="B17" s="98"/>
+      <c r="C17" s="92">
         <f>16742.23+2154.33</f>
         <v>18896.559999999998</v>
       </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="100"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="143"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="101">
+      <c r="B18" s="97"/>
+      <c r="C18" s="92">
         <v>76048</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="100"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="91"/>
       <c r="G18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="108"/>
-      <c r="C19" s="101">
+      <c r="B19" s="99"/>
+      <c r="C19" s="92">
         <v>258515.27</v>
       </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="100"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="91"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="106"/>
-      <c r="C20" s="101">
+      <c r="B20" s="97"/>
+      <c r="C20" s="92">
         <v>0</v>
       </c>
-      <c r="E20" s="97"/>
-      <c r="F20" s="100"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="91"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="109"/>
-      <c r="C21" s="102">
+      <c r="B21" s="100"/>
+      <c r="C21" s="93">
         <f>SUM(C12:C20)</f>
         <v>627830.20499999996</v>
       </c>
       <c r="D21" s="10"/>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="32">
         <f>SUM(F12:F19)</f>
-        <v>-711876.81022400619</v>
+        <v>-831053.26022400614</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="103"/>
+      <c r="B22" s="97"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="4"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
-      <c r="B23" s="106"/>
-      <c r="C23" s="110"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="97"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,7 +2030,7 @@
         <v>60</v>
       </c>
       <c r="B24" s="22"/>
-      <c r="C24" s="44">
+      <c r="C24" s="39">
         <f>SUM(C22:C23)</f>
         <v>0</v>
       </c>
@@ -2009,161 +2038,134 @@
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="73">
+      <c r="B25" s="26"/>
+      <c r="C25" s="68">
         <f>+C24+C21</f>
         <v>627830.20499999996</v>
       </c>
       <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="74"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="75"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="76">
+      <c r="B26" s="37"/>
+      <c r="C26" s="69"/>
+    </row>
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="70">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="76">
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="45">
+        <f>SUM(C27:C27)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="70">
+        <f>1200000-627830.21</f>
+        <v>572169.79</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="145">
+        <f>C29+C25</f>
+        <v>1199999.9950000001</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="77"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="114"/>
-      <c r="B32" s="114"/>
-      <c r="C32" s="76"/>
-    </row>
-    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="76">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="50">
-        <f>SUM(C29:C33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C35" s="76"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="78">
-        <f>C35+C25</f>
+      <c r="A31" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="34"/>
+      <c r="C31" s="45">
+        <f>+C25+C28</f>
         <v>627830.20499999996</v>
       </c>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="50">
-        <f>+C25+C34</f>
-        <v>627830.20499999996</v>
-      </c>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
       <c r="E37" s="10"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="13"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+      <c r="A58" s="11"/>
       <c r="B58" s="11"/>
-      <c r="C58" s="13"/>
+      <c r="C58" s="11"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2199,121 +2201,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="str">
+      <c r="A1" s="120" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="84" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="140" t="s">
+      <c r="F1" s="75"/>
+      <c r="G1" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="143">
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="118">
         <f>O1</f>
-        <v>1000000</v>
-      </c>
-      <c r="M1" s="144"/>
+        <v>1200000</v>
+      </c>
+      <c r="M1" s="119"/>
       <c r="O1" s="14">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="P1" s="14"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="str">
+      <c r="A2" s="77" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 15/05</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="46" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="96">
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="88">
         <v>413723.43999999994</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="134" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="124" t="s">
+      <c r="C3" s="132" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="124" t="s">
+      <c r="E3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="124" t="s">
+      <c r="F3" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="124" t="s">
+      <c r="G3" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="124" t="s">
+      <c r="H3" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="136" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="128" t="s">
+      <c r="J3" s="136" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="124" t="s">
+      <c r="K3" s="132" t="s">
         <v>63</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="87" t="s">
+      <c r="M3" s="79" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="127"/>
+      <c r="A4" s="135"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="125"/>
+      <c r="C4" s="133"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="80" t="str">
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="72" t="str">
         <f>A2</f>
         <v>Vto. 15/05</v>
       </c>
-      <c r="M4" s="87" t="s">
+      <c r="M4" s="79" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="86">
+      <c r="A5" s="78">
         <v>1</v>
       </c>
       <c r="B5" s="7">
@@ -2322,27 +2324,27 @@
       <c r="C5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="44">
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
         <v>210000</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="38">
         <f>E5</f>
         <v>210000</v>
       </c>
-      <c r="G5" s="81">
+      <c r="G5" s="73">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="82">
+      <c r="H5" s="74">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="23">
         <f>L$1*B5</f>
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="J5" s="9">
         <f>J$2*D5</f>
@@ -2351,43 +2353,43 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>210000</v>
-      </c>
-      <c r="M5" s="88">
+        <v>252000</v>
+      </c>
+      <c r="M5" s="80">
         <f>L5+L5*4%</f>
-        <v>218400</v>
+        <v>262080</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="86">
+      <c r="A6" s="78">
         <v>2</v>
       </c>
       <c r="B6" s="7">
         <v>0.16</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="44">
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
         <v>172074.00727995942</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="38">
         <v>0</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="73">
         <f t="shared" ref="G6:G9" si="1">E6-F6</f>
         <v>172074.00727995942</v>
       </c>
-      <c r="H6" s="82">
+      <c r="H6" s="74">
         <f t="shared" ref="H6:H9" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
         <v>14454.216611516593</v>
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
-        <v>160000</v>
+        <v>192000</v>
       </c>
       <c r="J6" s="9">
         <f>J$2*D6</f>
@@ -2396,57 +2398,57 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>346528.22389147605</v>
-      </c>
-      <c r="M6" s="88">
+        <v>378528.22389147605</v>
+      </c>
+      <c r="M6" s="80">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>360389.3528471351</v>
+        <v>393669.3528471351</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="86">
+      <c r="A7" s="78">
         <v>3</v>
       </c>
       <c r="B7" s="7">
         <v>0.21</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="49"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="23">
         <v>374690.18207680772</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="38">
         <v>0</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="73">
         <f t="shared" si="1"/>
         <v>374690.18207680772</v>
       </c>
-      <c r="H7" s="82">
+      <c r="H7" s="74">
         <f t="shared" si="2"/>
         <v>31473.975294451851</v>
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="J7" s="9">
         <v>0</v>
       </c>
-      <c r="K7" s="111"/>
+      <c r="K7" s="102"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
-        <v>616164.15737125953</v>
-      </c>
-      <c r="M7" s="88">
+        <v>658164.15737125953</v>
+      </c>
+      <c r="M7" s="80">
         <f t="shared" si="3"/>
-        <v>640810.72366610996</v>
+        <v>684490.72366610996</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
+      <c r="A8" s="78">
         <v>4</v>
       </c>
       <c r="B8" s="7">
@@ -2455,25 +2457,25 @@
       <c r="C8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="23">
         <v>210000</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="38">
         <f>E8</f>
         <v>210000</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="82">
+      <c r="H8" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="23">
         <f>L$1*B8</f>
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="J8" s="9">
         <v>0</v>
@@ -2481,15 +2483,15 @@
       <c r="K8" s="9"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>210000</v>
-      </c>
-      <c r="M8" s="88">
+        <v>252000</v>
+      </c>
+      <c r="M8" s="80">
         <f t="shared" si="3"/>
-        <v>218400</v>
+        <v>262080</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="78">
         <v>5</v>
       </c>
       <c r="B9" s="7">
@@ -2498,25 +2500,25 @@
       <c r="C9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="49"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="23">
         <v>210000</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="38">
         <f>E9</f>
         <v>210000</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="82">
+      <c r="H9" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="23">
         <f>L$1*B9</f>
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2524,106 +2526,106 @@
       <c r="K9" s="9"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>210000</v>
-      </c>
-      <c r="M9" s="88">
+        <v>252000</v>
+      </c>
+      <c r="M9" s="80">
         <f t="shared" si="3"/>
-        <v>218400</v>
+        <v>262080</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="89" t="s">
+      <c r="A10" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="90">
+      <c r="B10" s="82">
         <f>SUM(B5:B9)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="92">
+      <c r="C10" s="83"/>
+      <c r="D10" s="84">
         <f t="shared" ref="D10:J10" si="4">SUM(D5:D6)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="85">
         <f>SUM(E5:E9)</f>
         <v>1176764.1893567671</v>
       </c>
-      <c r="F10" s="93">
+      <c r="F10" s="85">
         <f>SUM(F5:F9)</f>
         <v>630000</v>
       </c>
-      <c r="G10" s="93">
+      <c r="G10" s="85">
         <f t="shared" si="4"/>
         <v>172074.00727995942</v>
       </c>
-      <c r="H10" s="93">
+      <c r="H10" s="85">
         <f t="shared" si="4"/>
         <v>14454.216611516593</v>
       </c>
-      <c r="I10" s="94">
+      <c r="I10" s="86">
         <f>SUM(I5:I9)</f>
-        <v>1000000</v>
-      </c>
-      <c r="J10" s="94">
+        <v>1200000</v>
+      </c>
+      <c r="J10" s="86">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K10" s="94"/>
-      <c r="L10" s="93">
+      <c r="K10" s="86"/>
+      <c r="L10" s="85">
         <f>SUM(L5:L9)</f>
-        <v>1592692.3812627355</v>
-      </c>
-      <c r="M10" s="95">
+        <v>1792692.3812627355</v>
+      </c>
+      <c r="M10" s="87">
         <f>SUM(M5:M9)</f>
-        <v>1656400.0765132452</v>
+        <v>1864400.0765132452</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="147"/>
-      <c r="B11" s="147"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="147"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="134" t="s">
+      <c r="C14" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="136" t="s">
+      <c r="C15" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
       <c r="R15" t="s">
         <v>30</v>
       </c>
@@ -2632,18 +2634,18 @@
       </c>
     </row>
     <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="54"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
       <c r="R16" t="s">
         <v>28</v>
       </c>
@@ -2652,20 +2654,20 @@
       </c>
     </row>
     <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59" t="s">
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
       <c r="R17" t="s">
         <v>31</v>
       </c>
@@ -2674,16 +2676,16 @@
       </c>
     </row>
     <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
       <c r="R18" t="s">
         <v>29</v>
       </c>
@@ -2692,30 +2694,30 @@
       </c>
     </row>
     <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="137" t="s">
+      <c r="C19" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="138"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="54"/>
     </row>
     <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="56"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="54"/>
       <c r="R20" t="s">
         <v>34</v>
       </c>
@@ -2724,1374 +2726,1378 @@
       </c>
     </row>
     <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59" t="str">
+      <c r="D21" s="54"/>
+      <c r="E21" s="54" t="str">
         <f>C5</f>
         <v>TARQUIRINI SABRINA</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59" t="s">
+      <c r="F21" s="54"/>
+      <c r="G21" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H21" s="62"/>
-      <c r="I21" s="132" t="s">
+      <c r="H21" s="57"/>
+      <c r="I21" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="133"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
     </row>
     <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="54">
         <f>A5</f>
         <v>1</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
     </row>
     <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="56"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="139"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
     </row>
     <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="68">
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="63">
         <f>L$1/5</f>
-        <v>200000</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
+        <v>240000</v>
+      </c>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
     </row>
     <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="68">
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="63">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
     </row>
     <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="68">
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="63">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="70" t="s">
+      <c r="C27" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="68">
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="63">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I27" s="56"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
     </row>
     <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="70" t="s">
+      <c r="C28" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="68">
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="63">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I28" s="56"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
     </row>
     <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="59"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
     </row>
     <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="68">
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="63">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I30" s="56"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="59"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
     </row>
     <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="56"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="59"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
     </row>
     <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="130" t="s">
+      <c r="C32" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="105">
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="96">
         <f>SUM(H24:H31)</f>
-        <v>245366.38250000001</v>
-      </c>
-      <c r="I32" s="66"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="59"/>
+        <v>285366.38250000001</v>
+      </c>
+      <c r="I32" s="61"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54"/>
     </row>
     <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="134" t="s">
+      <c r="C36" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="135"/>
-      <c r="E36" s="135"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="135"/>
-      <c r="H36" s="135"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="108"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="136" t="s">
+      <c r="C37" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="135"/>
-      <c r="E37" s="135"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="108"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
     </row>
     <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="54"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59" t="s">
+      <c r="C38" s="49"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="59"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
     </row>
     <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59" t="str">
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I39" s="56"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="59"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="60"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="59"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
     </row>
     <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="137" t="s">
+      <c r="C41" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="138"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="59"/>
+      <c r="D41" s="106"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="106"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
     </row>
     <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="56"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="56" t="s">
+      <c r="C43" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59" t="str">
+      <c r="D43" s="54"/>
+      <c r="E43" s="54" t="str">
         <f>C7</f>
         <v>LUCA BASUALDO</v>
       </c>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59" t="s">
+      <c r="F43" s="54"/>
+      <c r="G43" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H43" s="62"/>
-      <c r="I43" s="132" t="s">
+      <c r="H43" s="57"/>
+      <c r="I43" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="J43" s="133"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
+      <c r="J43" s="111"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
     </row>
     <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="56" t="s">
+      <c r="C44" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="63" t="s">
+      <c r="D44" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E44" s="59">
+      <c r="E44" s="54">
         <f>A7</f>
         <v>3</v>
       </c>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="59"/>
-      <c r="L44" s="59"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="54"/>
     </row>
     <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="56"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="71"/>
-      <c r="L45" s="71"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="112"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="66"/>
+      <c r="L45" s="66"/>
     </row>
     <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="68">
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="63">
         <f>L$1/5</f>
-        <v>200000</v>
-      </c>
-      <c r="I46" s="56"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="59"/>
-      <c r="L46" s="59"/>
+        <v>240000</v>
+      </c>
+      <c r="I46" s="51"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="54"/>
     </row>
     <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="56"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="59"/>
-      <c r="L47" s="59"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="56"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="64"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="59"/>
-      <c r="L48" s="59"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
     </row>
     <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="130" t="s">
+      <c r="C49" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="131"/>
-      <c r="E49" s="131"/>
-      <c r="F49" s="131"/>
-      <c r="G49" s="131"/>
-      <c r="H49" s="105">
+      <c r="D49" s="114"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="114"/>
+      <c r="H49" s="96">
         <f>M6</f>
-        <v>360389.3528471351</v>
-      </c>
-      <c r="I49" s="66"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="59"/>
-      <c r="L49" s="59"/>
+        <v>393669.3528471351</v>
+      </c>
+      <c r="I49" s="61"/>
+      <c r="J49" s="62"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
     </row>
     <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="134" t="s">
+      <c r="C52" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="135"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
-      <c r="I52" s="54"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="108"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="50"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="54"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="136" t="s">
+      <c r="C53" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="135"/>
-      <c r="E53" s="135"/>
-      <c r="F53" s="135"/>
-      <c r="G53" s="135"/>
-      <c r="H53" s="135"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="59"/>
-      <c r="L53" s="59"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="108"/>
+      <c r="G53" s="108"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
     </row>
     <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="54"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="59" t="s">
+      <c r="C54" s="49"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="I54" s="56"/>
-      <c r="J54" s="57"/>
-      <c r="K54" s="59"/>
-      <c r="L54" s="59"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
     </row>
     <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="56" t="s">
+      <c r="C55" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59" t="str">
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I55" s="56"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
     </row>
     <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="60"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="59"/>
-      <c r="L56" s="59"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="52"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
     </row>
     <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="137" t="s">
+      <c r="C57" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D57" s="138"/>
-      <c r="E57" s="138"/>
-      <c r="F57" s="138"/>
-      <c r="G57" s="138"/>
-      <c r="H57" s="138"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="57"/>
-      <c r="K57" s="59"/>
-      <c r="L57" s="59"/>
+      <c r="D57" s="106"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="106"/>
+      <c r="H57" s="106"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="54"/>
     </row>
     <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="56"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="59"/>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="57"/>
-      <c r="K58" s="59"/>
-      <c r="L58" s="59"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="54"/>
     </row>
     <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="56" t="s">
+      <c r="C59" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D59" s="59"/>
-      <c r="E59" s="59" t="str">
+      <c r="D59" s="54"/>
+      <c r="E59" s="54" t="str">
         <f>C6</f>
         <v>CASTILLO JONATHAN</v>
       </c>
-      <c r="F59" s="59"/>
-      <c r="G59" s="59" t="s">
+      <c r="F59" s="54"/>
+      <c r="G59" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H59" s="62"/>
-      <c r="I59" s="132" t="s">
+      <c r="H59" s="57"/>
+      <c r="I59" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="133"/>
-      <c r="K59" s="71"/>
-      <c r="L59" s="71"/>
+      <c r="J59" s="111"/>
+      <c r="K59" s="66"/>
+      <c r="L59" s="66"/>
     </row>
     <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="56" t="s">
+      <c r="C60" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="D60" s="63" t="s">
+      <c r="D60" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E60" s="59">
+      <c r="E60" s="54">
         <f>A6</f>
         <v>2</v>
       </c>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="59"/>
-      <c r="L60" s="59"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="51"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="56"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="139"/>
-      <c r="J61" s="133"/>
-      <c r="K61" s="71"/>
-      <c r="L61" s="71"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="112"/>
+      <c r="J61" s="111"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
     </row>
     <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="56" t="s">
+      <c r="C62" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D62" s="59"/>
-      <c r="E62" s="59"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="68">
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="63">
         <f>L$1/5</f>
-        <v>200000</v>
-      </c>
-      <c r="I62" s="56"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="59"/>
-      <c r="L62" s="59"/>
+        <v>240000</v>
+      </c>
+      <c r="I62" s="51"/>
+      <c r="J62" s="52"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="54"/>
     </row>
     <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="70" t="s">
+      <c r="C63" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="68">
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="63">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I63" s="56"/>
-      <c r="J63" s="57"/>
-      <c r="K63" s="59"/>
-      <c r="L63" s="59"/>
+      <c r="I63" s="51"/>
+      <c r="J63" s="52"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="54"/>
     </row>
     <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="70" t="s">
+      <c r="C64" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="68">
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="63">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I64" s="56"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="52"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="54"/>
     </row>
     <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="70" t="s">
+      <c r="C65" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D65" s="59"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="68">
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="63">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I65" s="56"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="59"/>
-      <c r="L65" s="59"/>
+      <c r="I65" s="51"/>
+      <c r="J65" s="52"/>
+      <c r="K65" s="54"/>
+      <c r="L65" s="54"/>
     </row>
     <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="70" t="s">
+      <c r="C66" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="68">
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
+      <c r="H66" s="63">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I66" s="56"/>
-      <c r="J66" s="57"/>
-      <c r="K66" s="59"/>
-      <c r="L66" s="59"/>
+      <c r="I66" s="51"/>
+      <c r="J66" s="52"/>
+      <c r="K66" s="54"/>
+      <c r="L66" s="54"/>
     </row>
     <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="56"/>
-      <c r="J67" s="57"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="59"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="52"/>
+      <c r="K67" s="54"/>
+      <c r="L67" s="54"/>
     </row>
     <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="70" t="s">
+      <c r="C68" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="59"/>
-      <c r="H68" s="68">
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="63">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I68" s="56"/>
-      <c r="J68" s="57"/>
-      <c r="K68" s="59"/>
-      <c r="L68" s="59"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="52"/>
+      <c r="K68" s="54"/>
+      <c r="L68" s="54"/>
     </row>
     <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="56"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="56"/>
-      <c r="J69" s="57"/>
-      <c r="K69" s="59"/>
-      <c r="L69" s="59"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="51"/>
+      <c r="J69" s="52"/>
+      <c r="K69" s="54"/>
+      <c r="L69" s="54"/>
     </row>
     <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="56"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="59"/>
-      <c r="F70" s="59"/>
-      <c r="G70" s="59"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="56"/>
-      <c r="J70" s="57"/>
-      <c r="K70" s="59"/>
-      <c r="L70" s="59"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="54"/>
+      <c r="L70" s="54"/>
     </row>
     <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="56"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59"/>
-      <c r="F71" s="59"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="64"/>
-      <c r="J71" s="65"/>
-      <c r="K71" s="59"/>
-      <c r="L71" s="59"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="59"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="54"/>
+      <c r="L71" s="54"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="130" t="s">
+      <c r="C72" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D72" s="131"/>
-      <c r="E72" s="131"/>
-      <c r="F72" s="131"/>
-      <c r="G72" s="131"/>
-      <c r="H72" s="105">
+      <c r="D72" s="114"/>
+      <c r="E72" s="114"/>
+      <c r="F72" s="114"/>
+      <c r="G72" s="114"/>
+      <c r="H72" s="96">
         <f>SUM(H62:H71)</f>
-        <v>245366.38250000001</v>
-      </c>
-      <c r="I72" s="66"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="59"/>
-      <c r="L72" s="59"/>
+        <v>285366.38250000001</v>
+      </c>
+      <c r="I72" s="61"/>
+      <c r="J72" s="62"/>
+      <c r="K72" s="54"/>
+      <c r="L72" s="54"/>
     </row>
     <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="134" t="s">
+      <c r="C76" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D76" s="135"/>
-      <c r="E76" s="135"/>
-      <c r="F76" s="135"/>
-      <c r="G76" s="135"/>
-      <c r="H76" s="135"/>
-      <c r="I76" s="54"/>
-      <c r="J76" s="55"/>
-      <c r="K76" s="59"/>
-      <c r="L76" s="59"/>
+      <c r="D76" s="108"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="108"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="50"/>
+      <c r="K76" s="54"/>
+      <c r="L76" s="54"/>
     </row>
     <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="136" t="s">
+      <c r="C77" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="135"/>
-      <c r="E77" s="135"/>
-      <c r="F77" s="135"/>
-      <c r="G77" s="135"/>
-      <c r="H77" s="135"/>
-      <c r="I77" s="56"/>
-      <c r="J77" s="57"/>
-      <c r="K77" s="59"/>
-      <c r="L77" s="59"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="108"/>
+      <c r="F77" s="108"/>
+      <c r="G77" s="108"/>
+      <c r="H77" s="108"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="54"/>
+      <c r="L77" s="54"/>
     </row>
     <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="54"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="59"/>
-      <c r="H78" s="59" t="s">
+      <c r="C78" s="49"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="I78" s="56"/>
-      <c r="J78" s="57"/>
-      <c r="K78" s="59"/>
-      <c r="L78" s="59"/>
+      <c r="I78" s="51"/>
+      <c r="J78" s="52"/>
+      <c r="K78" s="54"/>
+      <c r="L78" s="54"/>
     </row>
     <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C79" s="56" t="s">
+      <c r="C79" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="59"/>
-      <c r="F79" s="59"/>
-      <c r="G79" s="59"/>
-      <c r="H79" s="59" t="str">
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I79" s="56"/>
-      <c r="J79" s="57"/>
-      <c r="K79" s="59"/>
-      <c r="L79" s="59"/>
+      <c r="I79" s="51"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="54"/>
+      <c r="L79" s="54"/>
     </row>
     <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="60"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="56"/>
-      <c r="J80" s="57"/>
-      <c r="K80" s="59"/>
-      <c r="L80" s="59"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="56"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="56"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="51"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="54"/>
+      <c r="L80" s="54"/>
     </row>
     <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="137" t="s">
+      <c r="C81" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D81" s="138"/>
-      <c r="E81" s="138"/>
-      <c r="F81" s="138"/>
-      <c r="G81" s="138"/>
-      <c r="H81" s="138"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="57"/>
-      <c r="K81" s="59"/>
-      <c r="L81" s="59"/>
+      <c r="D81" s="106"/>
+      <c r="E81" s="106"/>
+      <c r="F81" s="106"/>
+      <c r="G81" s="106"/>
+      <c r="H81" s="106"/>
+      <c r="I81" s="51"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="54"/>
+      <c r="L81" s="54"/>
     </row>
     <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="56"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="56"/>
-      <c r="J82" s="57"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
+      <c r="C82" s="51"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="54"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="54"/>
+      <c r="L82" s="54"/>
     </row>
     <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="56" t="s">
+      <c r="C83" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="59" t="str">
+      <c r="D83" s="54"/>
+      <c r="E83" s="54" t="str">
         <f>C8</f>
         <v xml:space="preserve">JOHANA </v>
       </c>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59" t="s">
+      <c r="F83" s="54"/>
+      <c r="G83" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H83" s="62"/>
-      <c r="I83" s="132" t="s">
+      <c r="H83" s="57"/>
+      <c r="I83" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="J83" s="133"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
+      <c r="J83" s="111"/>
+      <c r="K83" s="66"/>
+      <c r="L83" s="66"/>
     </row>
     <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="56" t="s">
+      <c r="C84" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="D84" s="63" t="s">
+      <c r="D84" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="59">
+      <c r="E84" s="54">
         <f>A8</f>
         <v>4</v>
       </c>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="56"/>
-      <c r="J84" s="57"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="52"/>
+      <c r="K84" s="54"/>
+      <c r="L84" s="54"/>
     </row>
     <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="56"/>
-      <c r="D85" s="59"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="139"/>
-      <c r="J85" s="133"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
+      <c r="C85" s="51"/>
+      <c r="D85" s="54"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="54"/>
+      <c r="I85" s="112"/>
+      <c r="J85" s="111"/>
+      <c r="K85" s="66"/>
+      <c r="L85" s="66"/>
     </row>
     <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="56" t="s">
+      <c r="C86" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D86" s="59"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="68">
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="63">
         <f>L$1/5</f>
-        <v>200000</v>
-      </c>
-      <c r="I86" s="56"/>
-      <c r="J86" s="57"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
+        <v>240000</v>
+      </c>
+      <c r="I86" s="51"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="54"/>
+      <c r="L86" s="54"/>
     </row>
     <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="70" t="s">
+      <c r="C87" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D87" s="59"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="68">
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="63">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I87" s="56"/>
-      <c r="J87" s="57"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="54"/>
+      <c r="L87" s="54"/>
     </row>
     <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="70" t="s">
+      <c r="C88" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D88" s="59"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="68">
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="63">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I88" s="56"/>
-      <c r="J88" s="57"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="54"/>
+      <c r="L88" s="54"/>
     </row>
     <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C89" s="70" t="s">
+      <c r="C89" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D89" s="59"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="68">
+      <c r="D89" s="54"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="63">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I89" s="56"/>
-      <c r="J89" s="57"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="54"/>
+      <c r="L89" s="54"/>
     </row>
     <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C90" s="70" t="s">
+      <c r="C90" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D90" s="59"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="68">
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="63">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I90" s="56"/>
-      <c r="J90" s="57"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="52"/>
+      <c r="K90" s="54"/>
+      <c r="L90" s="54"/>
     </row>
     <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D91" s="59"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="68"/>
-      <c r="I91" s="56"/>
-      <c r="J91" s="57"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="52"/>
+      <c r="K91" s="54"/>
+      <c r="L91" s="54"/>
     </row>
     <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="70" t="s">
+      <c r="C92" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="68">
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="63">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I92" s="64"/>
-      <c r="J92" s="65"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
+      <c r="I92" s="59"/>
+      <c r="J92" s="60"/>
+      <c r="K92" s="54"/>
+      <c r="L92" s="54"/>
     </row>
     <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D93" s="59"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="56"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="54"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="54"/>
+      <c r="L93" s="54"/>
     </row>
     <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="130" t="s">
+      <c r="C94" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="131"/>
-      <c r="E94" s="131"/>
-      <c r="F94" s="131"/>
-      <c r="G94" s="131"/>
-      <c r="H94" s="105">
+      <c r="D94" s="114"/>
+      <c r="E94" s="114"/>
+      <c r="F94" s="114"/>
+      <c r="G94" s="114"/>
+      <c r="H94" s="96">
         <f>SUM(H86:H93)</f>
-        <v>245366.38250000001</v>
-      </c>
-      <c r="I94" s="66"/>
-      <c r="J94" s="67"/>
-      <c r="K94" s="59"/>
-      <c r="L94" s="59"/>
+        <v>285366.38250000001</v>
+      </c>
+      <c r="I94" s="61"/>
+      <c r="J94" s="62"/>
+      <c r="K94" s="54"/>
+      <c r="L94" s="54"/>
     </row>
     <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="134" t="s">
+      <c r="C98" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D98" s="135"/>
-      <c r="E98" s="135"/>
-      <c r="F98" s="135"/>
-      <c r="G98" s="135"/>
-      <c r="H98" s="135"/>
-      <c r="I98" s="54"/>
-      <c r="J98" s="55"/>
-      <c r="K98" s="59"/>
-      <c r="L98" s="59"/>
+      <c r="D98" s="108"/>
+      <c r="E98" s="108"/>
+      <c r="F98" s="108"/>
+      <c r="G98" s="108"/>
+      <c r="H98" s="108"/>
+      <c r="I98" s="49"/>
+      <c r="J98" s="50"/>
+      <c r="K98" s="54"/>
+      <c r="L98" s="54"/>
     </row>
     <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="136" t="s">
+      <c r="C99" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="135"/>
-      <c r="E99" s="135"/>
-      <c r="F99" s="135"/>
-      <c r="G99" s="135"/>
-      <c r="H99" s="135"/>
-      <c r="I99" s="56"/>
-      <c r="J99" s="57"/>
-      <c r="K99" s="59"/>
-      <c r="L99" s="59"/>
+      <c r="D99" s="108"/>
+      <c r="E99" s="108"/>
+      <c r="F99" s="108"/>
+      <c r="G99" s="108"/>
+      <c r="H99" s="108"/>
+      <c r="I99" s="51"/>
+      <c r="J99" s="52"/>
+      <c r="K99" s="54"/>
+      <c r="L99" s="54"/>
     </row>
     <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C100" s="54"/>
-      <c r="D100" s="58"/>
-      <c r="E100" s="58"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="59"/>
-      <c r="H100" s="59" t="s">
+      <c r="C100" s="49"/>
+      <c r="D100" s="53"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="I100" s="56"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="59"/>
-      <c r="L100" s="59"/>
+      <c r="I100" s="51"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="54"/>
+      <c r="L100" s="54"/>
     </row>
     <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="56" t="s">
+      <c r="C101" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="D101" s="59"/>
-      <c r="E101" s="59"/>
-      <c r="F101" s="59"/>
-      <c r="G101" s="59"/>
-      <c r="H101" s="59" t="str">
+      <c r="D101" s="54"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="54"/>
+      <c r="H101" s="54" t="str">
         <f>H17</f>
         <v>VENCIMIENTO: DICIEMBRE</v>
       </c>
-      <c r="I101" s="56"/>
-      <c r="J101" s="57"/>
-      <c r="K101" s="59"/>
-      <c r="L101" s="59"/>
+      <c r="I101" s="51"/>
+      <c r="J101" s="52"/>
+      <c r="K101" s="54"/>
+      <c r="L101" s="54"/>
     </row>
     <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C102" s="60"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61"/>
-      <c r="I102" s="56"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="59"/>
-      <c r="L102" s="59"/>
+      <c r="C102" s="55"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="56"/>
+      <c r="G102" s="56"/>
+      <c r="H102" s="56"/>
+      <c r="I102" s="51"/>
+      <c r="J102" s="52"/>
+      <c r="K102" s="54"/>
+      <c r="L102" s="54"/>
     </row>
     <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="137" t="s">
+      <c r="C103" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="D103" s="138"/>
-      <c r="E103" s="138"/>
-      <c r="F103" s="138"/>
-      <c r="G103" s="138"/>
-      <c r="H103" s="138"/>
-      <c r="I103" s="56"/>
-      <c r="J103" s="57"/>
-      <c r="K103" s="59"/>
-      <c r="L103" s="59"/>
+      <c r="D103" s="106"/>
+      <c r="E103" s="106"/>
+      <c r="F103" s="106"/>
+      <c r="G103" s="106"/>
+      <c r="H103" s="106"/>
+      <c r="I103" s="51"/>
+      <c r="J103" s="52"/>
+      <c r="K103" s="54"/>
+      <c r="L103" s="54"/>
     </row>
     <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C104" s="56"/>
-      <c r="D104" s="59"/>
-      <c r="E104" s="59"/>
-      <c r="F104" s="59"/>
-      <c r="G104" s="59"/>
-      <c r="H104" s="59"/>
-      <c r="I104" s="56"/>
-      <c r="J104" s="57"/>
-      <c r="K104" s="59"/>
-      <c r="L104" s="59"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="54"/>
+      <c r="I104" s="51"/>
+      <c r="J104" s="52"/>
+      <c r="K104" s="54"/>
+      <c r="L104" s="54"/>
     </row>
     <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C105" s="56" t="s">
+      <c r="C105" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="D105" s="59"/>
-      <c r="E105" s="59" t="str">
+      <c r="D105" s="54"/>
+      <c r="E105" s="54" t="str">
         <f>C9</f>
         <v xml:space="preserve">VARLAS GUILLERMO </v>
       </c>
-      <c r="F105" s="59"/>
-      <c r="G105" s="59" t="s">
+      <c r="F105" s="54"/>
+      <c r="G105" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="H105" s="62"/>
-      <c r="I105" s="132" t="s">
+      <c r="H105" s="57"/>
+      <c r="I105" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="J105" s="133"/>
-      <c r="K105" s="71"/>
-      <c r="L105" s="71"/>
+      <c r="J105" s="111"/>
+      <c r="K105" s="66"/>
+      <c r="L105" s="66"/>
     </row>
     <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C106" s="56" t="s">
+      <c r="C106" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="D106" s="63" t="s">
+      <c r="D106" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E106" s="59">
+      <c r="E106" s="54">
         <v>5</v>
       </c>
-      <c r="F106" s="59"/>
-      <c r="G106" s="59"/>
-      <c r="H106" s="59"/>
-      <c r="I106" s="56"/>
-      <c r="J106" s="57"/>
-      <c r="K106" s="59"/>
-      <c r="L106" s="59"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="54"/>
+      <c r="H106" s="54"/>
+      <c r="I106" s="51"/>
+      <c r="J106" s="52"/>
+      <c r="K106" s="54"/>
+      <c r="L106" s="54"/>
     </row>
     <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C107" s="56"/>
-      <c r="D107" s="59"/>
-      <c r="E107" s="59"/>
-      <c r="F107" s="59"/>
-      <c r="G107" s="59"/>
-      <c r="H107" s="59"/>
-      <c r="I107" s="139"/>
-      <c r="J107" s="133"/>
-      <c r="K107" s="71"/>
-      <c r="L107" s="71"/>
+      <c r="C107" s="51"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="54"/>
+      <c r="H107" s="54"/>
+      <c r="I107" s="112"/>
+      <c r="J107" s="111"/>
+      <c r="K107" s="66"/>
+      <c r="L107" s="66"/>
     </row>
     <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C108" s="56" t="s">
+      <c r="C108" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D108" s="59"/>
-      <c r="E108" s="59"/>
-      <c r="F108" s="59"/>
-      <c r="G108" s="59"/>
-      <c r="H108" s="68">
+      <c r="D108" s="54"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="63">
         <f>L$1/5</f>
-        <v>200000</v>
-      </c>
-      <c r="I108" s="56"/>
-      <c r="J108" s="57"/>
-      <c r="K108" s="59"/>
-      <c r="L108" s="59"/>
+        <v>240000</v>
+      </c>
+      <c r="I108" s="51"/>
+      <c r="J108" s="52"/>
+      <c r="K108" s="54"/>
+      <c r="L108" s="54"/>
     </row>
     <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C109" s="70" t="s">
+      <c r="C109" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D109" s="59"/>
-      <c r="E109" s="59"/>
-      <c r="F109" s="59"/>
-      <c r="G109" s="59"/>
-      <c r="H109" s="68">
+      <c r="D109" s="54"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="63">
         <f>T$15/4</f>
         <v>24137.5</v>
       </c>
-      <c r="I109" s="56"/>
-      <c r="J109" s="57"/>
-      <c r="K109" s="59"/>
-      <c r="L109" s="59"/>
+      <c r="I109" s="51"/>
+      <c r="J109" s="52"/>
+      <c r="K109" s="54"/>
+      <c r="L109" s="54"/>
     </row>
     <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C110" s="70" t="s">
+      <c r="C110" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D110" s="59"/>
-      <c r="E110" s="59"/>
-      <c r="F110" s="59"/>
-      <c r="G110" s="59"/>
-      <c r="H110" s="68">
+      <c r="D110" s="54"/>
+      <c r="E110" s="54"/>
+      <c r="F110" s="54"/>
+      <c r="G110" s="54"/>
+      <c r="H110" s="63">
         <f>T$16/4</f>
         <v>6997.9375</v>
       </c>
-      <c r="I110" s="56"/>
-      <c r="J110" s="57"/>
-      <c r="K110" s="59"/>
-      <c r="L110" s="59"/>
+      <c r="I110" s="51"/>
+      <c r="J110" s="52"/>
+      <c r="K110" s="54"/>
+      <c r="L110" s="54"/>
     </row>
     <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C111" s="70" t="s">
+      <c r="C111" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D111" s="59"/>
-      <c r="E111" s="59"/>
-      <c r="F111" s="59"/>
-      <c r="G111" s="59"/>
-      <c r="H111" s="68">
+      <c r="D111" s="54"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="54"/>
+      <c r="H111" s="63">
         <f>T$17/4</f>
         <v>8000</v>
       </c>
-      <c r="I111" s="56"/>
-      <c r="J111" s="57"/>
-      <c r="K111" s="59"/>
-      <c r="L111" s="59"/>
+      <c r="I111" s="51"/>
+      <c r="J111" s="52"/>
+      <c r="K111" s="54"/>
+      <c r="L111" s="54"/>
     </row>
     <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C112" s="70" t="s">
+      <c r="C112" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D112" s="59"/>
-      <c r="E112" s="59"/>
-      <c r="F112" s="59"/>
-      <c r="G112" s="59"/>
-      <c r="H112" s="68">
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="63">
         <f>T$18/4</f>
         <v>6230.9449999999997</v>
       </c>
-      <c r="I112" s="56"/>
-      <c r="J112" s="57"/>
-      <c r="K112" s="59"/>
-      <c r="L112" s="59"/>
+      <c r="I112" s="51"/>
+      <c r="J112" s="52"/>
+      <c r="K112" s="54"/>
+      <c r="L112" s="54"/>
     </row>
     <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D113" s="59"/>
-      <c r="E113" s="59"/>
-      <c r="F113" s="59"/>
-      <c r="G113" s="59"/>
-      <c r="H113" s="68"/>
-      <c r="I113" s="56"/>
-      <c r="J113" s="57"/>
-      <c r="K113" s="59"/>
-      <c r="L113" s="59"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="63"/>
+      <c r="I113" s="51"/>
+      <c r="J113" s="52"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="54"/>
     </row>
     <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C114" s="70" t="s">
+      <c r="C114" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D114" s="59"/>
-      <c r="E114" s="59"/>
-      <c r="F114" s="59"/>
-      <c r="G114" s="59"/>
-      <c r="H114" s="68">
+      <c r="D114" s="54"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="54"/>
+      <c r="H114" s="63">
         <f>T$20/3</f>
         <v>0</v>
       </c>
-      <c r="I114" s="64"/>
-      <c r="J114" s="65"/>
-      <c r="K114" s="59"/>
-      <c r="L114" s="59"/>
+      <c r="I114" s="59"/>
+      <c r="J114" s="60"/>
+      <c r="K114" s="54"/>
+      <c r="L114" s="54"/>
     </row>
     <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D115" s="59"/>
-      <c r="E115" s="59"/>
-      <c r="F115" s="59"/>
-      <c r="G115" s="59"/>
-      <c r="H115" s="59"/>
-      <c r="I115" s="56"/>
-      <c r="J115" s="57"/>
-      <c r="K115" s="59"/>
-      <c r="L115" s="59"/>
+      <c r="D115" s="54"/>
+      <c r="E115" s="54"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="54"/>
+      <c r="H115" s="54"/>
+      <c r="I115" s="51"/>
+      <c r="J115" s="52"/>
+      <c r="K115" s="54"/>
+      <c r="L115" s="54"/>
     </row>
     <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="130" t="s">
+      <c r="C116" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="D116" s="131"/>
-      <c r="E116" s="131"/>
-      <c r="F116" s="131"/>
-      <c r="G116" s="131"/>
-      <c r="H116" s="105">
+      <c r="D116" s="114"/>
+      <c r="E116" s="114"/>
+      <c r="F116" s="114"/>
+      <c r="G116" s="114"/>
+      <c r="H116" s="96">
         <f>SUM(H108:H115)</f>
-        <v>245366.38250000001</v>
-      </c>
-      <c r="I116" s="66"/>
-      <c r="J116" s="67"/>
-      <c r="K116" s="59"/>
-      <c r="L116" s="59"/>
+        <v>285366.38250000001</v>
+      </c>
+      <c r="I116" s="61"/>
+      <c r="J116" s="62"/>
+      <c r="K116" s="54"/>
+      <c r="L116" s="54"/>
     </row>
     <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="115" t="s">
+      <c r="A119" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="B119" s="116"/>
-      <c r="C119" s="116"/>
-      <c r="D119" s="116"/>
-      <c r="E119" s="116"/>
-      <c r="F119" s="116"/>
-      <c r="G119" s="116"/>
-      <c r="H119" s="116"/>
-      <c r="I119" s="116"/>
-      <c r="J119" s="116"/>
-      <c r="K119" s="116"/>
-      <c r="L119" s="116"/>
-      <c r="M119" s="117"/>
+      <c r="B119" s="124"/>
+      <c r="C119" s="124"/>
+      <c r="D119" s="124"/>
+      <c r="E119" s="124"/>
+      <c r="F119" s="124"/>
+      <c r="G119" s="124"/>
+      <c r="H119" s="124"/>
+      <c r="I119" s="124"/>
+      <c r="J119" s="124"/>
+      <c r="K119" s="124"/>
+      <c r="L119" s="124"/>
+      <c r="M119" s="125"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="118"/>
-      <c r="B120" s="119"/>
-      <c r="C120" s="119"/>
-      <c r="D120" s="119"/>
-      <c r="E120" s="119"/>
-      <c r="F120" s="119"/>
-      <c r="G120" s="119"/>
-      <c r="H120" s="119"/>
-      <c r="I120" s="119"/>
-      <c r="J120" s="119"/>
-      <c r="K120" s="119"/>
-      <c r="L120" s="119"/>
-      <c r="M120" s="120"/>
+      <c r="A120" s="126"/>
+      <c r="B120" s="127"/>
+      <c r="C120" s="127"/>
+      <c r="D120" s="127"/>
+      <c r="E120" s="127"/>
+      <c r="F120" s="127"/>
+      <c r="G120" s="127"/>
+      <c r="H120" s="127"/>
+      <c r="I120" s="127"/>
+      <c r="J120" s="127"/>
+      <c r="K120" s="127"/>
+      <c r="L120" s="127"/>
+      <c r="M120" s="128"/>
     </row>
     <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="121"/>
-      <c r="B121" s="122"/>
-      <c r="C121" s="122"/>
-      <c r="D121" s="122"/>
-      <c r="E121" s="122"/>
-      <c r="F121" s="122"/>
-      <c r="G121" s="122"/>
-      <c r="H121" s="122"/>
-      <c r="I121" s="122"/>
-      <c r="J121" s="122"/>
-      <c r="K121" s="122"/>
-      <c r="L121" s="122"/>
-      <c r="M121" s="123"/>
+      <c r="A121" s="129"/>
+      <c r="B121" s="130"/>
+      <c r="C121" s="130"/>
+      <c r="D121" s="130"/>
+      <c r="E121" s="130"/>
+      <c r="F121" s="130"/>
+      <c r="G121" s="130"/>
+      <c r="H121" s="130"/>
+      <c r="I121" s="130"/>
+      <c r="J121" s="130"/>
+      <c r="K121" s="130"/>
+      <c r="L121" s="130"/>
+      <c r="M121" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="A119:M121"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C53:H53"/>
+    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="I107:J107"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -4108,25 +4114,21 @@
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="A119:M121"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C53:H53"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
+++ b/2026/URIARTE 630/Abril/EXPENSAS-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\URIARTE 630\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E106F5-83E8-48E8-BB86-5FBCB927A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB65D1A-824F-44A4-AC4C-1689F5CDB1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -21,11 +21,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -104,9 +99,6 @@
     <t>GASTOS ORDINARIOS A PRORRATEAR:</t>
   </si>
   <si>
-    <t>GASTOS EXTRAORDINARIOS A PRORRATEAR:</t>
-  </si>
-  <si>
     <t>Total gastos ordinarios a prorratear</t>
   </si>
   <si>
@@ -215,9 +207,6 @@
     <t>SUBTOTAL</t>
   </si>
   <si>
-    <t>Expensas extraordinarias</t>
-  </si>
-  <si>
     <t>Expensas ordinarias</t>
   </si>
   <si>
@@ -246,6 +235,12 @@
   </si>
   <si>
     <t>Prevision ordinaria</t>
+  </si>
+  <si>
+    <t>EDESUR:</t>
+  </si>
+  <si>
+    <t>Edesur</t>
   </si>
 </sst>
 </file>
@@ -258,9 +253,9 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="172" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,13 +364,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -438,7 +426,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -1130,13 +1118,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1253,7 +1254,6 @@
     <xf numFmtId="166" fontId="1" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1272,18 +1272,79 @@
     <xf numFmtId="16" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="6" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1291,13 +1352,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1322,71 +1381,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="1" fillId="6" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1465,9 +1471,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1505,9 +1511,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1540,26 +1546,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1592,26 +1581,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1789,56 +1761,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1846,29 +1818,29 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="103" t="s">
+      <c r="E11" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="104"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="105"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="97"/>
-      <c r="C12" s="92">
+        <v>31</v>
+      </c>
+      <c r="B12" s="96"/>
+      <c r="C12" s="91">
         <f>86199+86199*6%</f>
         <v>91370.94</v>
       </c>
@@ -1880,123 +1852,123 @@
         <v>-714046.60522400623</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="92">
+        <v>32</v>
+      </c>
+      <c r="B13" s="96"/>
+      <c r="C13" s="91">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="90">
+      <c r="E13" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="89">
         <f>'prorrateo '!F10</f>
         <v>630000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="97"/>
+        <v>45</v>
+      </c>
+      <c r="B14" s="96"/>
       <c r="C14" s="38">
         <v>0</v>
       </c>
       <c r="D14" s="24"/>
-      <c r="E14" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="144">
+      <c r="E14" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="102">
         <f>-C25</f>
         <v>-627830.20499999996</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="97"/>
+        <v>50</v>
+      </c>
+      <c r="B15" s="96"/>
       <c r="C15" s="38">
         <v>162057</v>
       </c>
       <c r="D15" s="24"/>
-      <c r="E15" s="138" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="141">
+      <c r="E15" s="106" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="109">
         <v>-119176.45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="92">
+        <v>66</v>
+      </c>
+      <c r="B16" s="97"/>
+      <c r="C16" s="91">
         <f>16422.66</f>
         <v>16422.66</v>
       </c>
-      <c r="E16" s="140"/>
-      <c r="F16" s="142"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="107"/>
+      <c r="F16" s="110"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="92">
+        <v>65</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="91">
         <f>16742.23+2154.33</f>
         <v>18896.559999999998</v>
       </c>
-      <c r="E17" s="139"/>
-      <c r="F17" s="143"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E17" s="108"/>
+      <c r="F17" s="111"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="92">
+        <v>30</v>
+      </c>
+      <c r="B18" s="96"/>
+      <c r="C18" s="91">
         <v>76048</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="91"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="90"/>
       <c r="G18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="92">
+        <v>28</v>
+      </c>
+      <c r="B19" s="98"/>
+      <c r="C19" s="91">
         <v>258515.27</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="91"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E19" s="88"/>
+      <c r="F19" s="90"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="97"/>
-      <c r="C20" s="92">
+        <v>56</v>
+      </c>
+      <c r="B20" s="96"/>
+      <c r="C20" s="91">
         <v>0</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="91"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="88"/>
+      <c r="F20" s="90"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="100"/>
-      <c r="C21" s="93">
+        <v>59</v>
+      </c>
+      <c r="B21" s="99"/>
+      <c r="C21" s="92">
         <f>SUM(C12:C20)</f>
         <v>627830.20499999996</v>
       </c>
@@ -2009,25 +1981,25 @@
         <v>-831053.26022400614</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="97"/>
-      <c r="C22" s="94"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="4"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="47"/>
-      <c r="B23" s="97"/>
-      <c r="C23" s="101"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="100"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="39">
@@ -2037,7 +2009,7 @@
       <c r="D24" s="4"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>11</v>
       </c>
@@ -2048,14 +2020,14 @@
       </c>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="37"/>
       <c r="C26" s="69"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="27"/>
       <c r="C27" s="70">
@@ -2063,7 +2035,7 @@
       </c>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>17</v>
       </c>
@@ -2073,9 +2045,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29" s="70">
         <f>1200000-627830.21</f>
@@ -2083,17 +2055,17 @@
       </c>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="145">
+        <v>24</v>
+      </c>
+      <c r="C30" s="103">
         <f>C29+C25</f>
         <v>1199999.9950000001</v>
       </c>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>12</v>
       </c>
@@ -2104,59 +2076,59 @@
       </c>
       <c r="E31" s="10"/>
     </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D36" s="5"/>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
     </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D39" s="10"/>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D40" s="10"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="12"/>
       <c r="B52" s="11"/>
       <c r="C52" s="13"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
@@ -2183,53 +2155,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="14"/>
+    <col min="11" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="140" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
       <c r="D1" s="75"/>
       <c r="E1" s="76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F1" s="75"/>
-      <c r="G1" s="115" t="s">
+      <c r="G1" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="118">
-        <f>O1</f>
-        <v>1200000</v>
-      </c>
-      <c r="M1" s="119"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="138">
+        <f>O1-L2</f>
+        <v>941484.73</v>
+      </c>
+      <c r="M1" s="139"/>
       <c r="O1" s="14">
         <v>1200000</v>
       </c>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="77" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 15/05</v>
@@ -2240,81 +2212,81 @@
       <c r="E2" s="41"/>
       <c r="F2" s="42"/>
       <c r="G2" s="41" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="67"/>
       <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="88">
-        <v>413723.43999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="134" t="s">
+      <c r="L2" s="143">
+        <v>258515.27</v>
+      </c>
+      <c r="M2" s="144"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="123" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="s">
+      <c r="C3" s="121" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="132" t="s">
+      <c r="E3" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="132" t="s">
+      <c r="F3" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="132" t="s">
+      <c r="G3" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="132" t="s">
+      <c r="H3" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="136" t="s">
+      <c r="I3" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="145" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="132" t="s">
-        <v>63</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M3" s="79" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="135"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="124"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="133"/>
+      <c r="C4" s="122"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="133"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="122"/>
       <c r="L4" s="72" t="str">
         <f>A2</f>
         <v>Vto. 15/05</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="78">
         <v>1</v>
       </c>
@@ -2322,7 +2294,7 @@
         <v>0.21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="44">
         <v>0.5</v>
@@ -2344,7 +2316,7 @@
       </c>
       <c r="I5" s="23">
         <f>L$1*B5</f>
-        <v>252000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="J5" s="9">
         <f>J$2*D5</f>
@@ -2353,14 +2325,14 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>252000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="M5" s="80">
         <f>L5+L5*4%</f>
-        <v>262080</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>205620.265032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="78">
         <v>2</v>
       </c>
@@ -2368,7 +2340,7 @@
         <v>0.16</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="44">
         <v>0.5</v>
@@ -2389,11 +2361,11 @@
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
-        <v>192000</v>
+        <v>150637.55679999999</v>
       </c>
       <c r="J6" s="9">
-        <f>J$2*D6</f>
-        <v>0</v>
+        <f>L$2*B6</f>
+        <v>41362.443200000002</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9">
@@ -2405,7 +2377,7 @@
         <v>393669.3528471351</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="78">
         <v>3</v>
       </c>
@@ -2413,7 +2385,7 @@
         <v>0.21</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="23">
@@ -2432,12 +2404,13 @@
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
-        <v>252000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="102"/>
+        <f t="shared" ref="J7:J9" si="4">L$2*B7</f>
+        <v>54288.206699999995</v>
+      </c>
+      <c r="K7" s="101"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
         <v>658164.15737125953</v>
@@ -2447,7 +2420,7 @@
         <v>684490.72366610996</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="78">
         <v>4</v>
       </c>
@@ -2455,7 +2428,7 @@
         <v>0.21</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="23">
@@ -2475,10 +2448,11 @@
       </c>
       <c r="I8" s="23">
         <f>L$1*B8</f>
-        <v>252000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="J8" s="9">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>54288.206699999995</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9">
@@ -2490,7 +2464,7 @@
         <v>262080</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="78">
         <v>5</v>
       </c>
@@ -2498,7 +2472,7 @@
         <v>0.21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="23">
@@ -2518,10 +2492,11 @@
       </c>
       <c r="I9" s="23">
         <f>L$1*B9</f>
-        <v>252000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="J9" s="9">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>54288.206699999995</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
@@ -2533,7 +2508,7 @@
         <v>262080</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="81" t="s">
         <v>7</v>
       </c>
@@ -2543,7 +2518,7 @@
       </c>
       <c r="C10" s="83"/>
       <c r="D10" s="84">
-        <f t="shared" ref="D10:J10" si="4">SUM(D5:D6)</f>
+        <f t="shared" ref="D10:J10" si="5">SUM(D5:D6)</f>
         <v>1</v>
       </c>
       <c r="E10" s="85">
@@ -2555,127 +2530,127 @@
         <v>630000</v>
       </c>
       <c r="G10" s="85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>172074.00727995942</v>
       </c>
       <c r="H10" s="85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14454.216611516593</v>
       </c>
       <c r="I10" s="86">
         <f>SUM(I5:I9)</f>
-        <v>1200000</v>
+        <v>941484.73</v>
       </c>
       <c r="J10" s="86">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>SUM(J5:J9)</f>
+        <v>204227.06329999998</v>
       </c>
       <c r="K10" s="86"/>
       <c r="L10" s="85">
         <f>SUM(L5:L9)</f>
-        <v>1792692.3812627355</v>
+        <v>1738404.1745627355</v>
       </c>
       <c r="M10" s="87">
         <f>SUM(M5:M9)</f>
-        <v>1864400.0765132452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-    </row>
-    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1807940.3415452451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="142"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
       <c r="I14" s="49"/>
       <c r="J14" s="50"/>
       <c r="K14" s="54"/>
       <c r="L14" s="54"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
+    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
       <c r="I15" s="51"/>
       <c r="J15" s="52"/>
       <c r="K15" s="54"/>
       <c r="L15" s="54"/>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T15">
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" s="49"/>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="54"/>
       <c r="H16" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" s="51"/>
       <c r="J16" s="52"/>
       <c r="K16" s="54"/>
       <c r="L16" s="54"/>
       <c r="R16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T16">
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
       <c r="F17" s="54"/>
       <c r="G17" s="54"/>
       <c r="H17" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="52"/>
       <c r="K17" s="54"/>
       <c r="L17" s="54"/>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T17">
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" s="55"/>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
@@ -2687,27 +2662,27 @@
       <c r="K18" s="54"/>
       <c r="L18" s="54"/>
       <c r="R18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T18">
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="132" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
       <c r="I19" s="51"/>
       <c r="J19" s="52"/>
       <c r="K19" s="54"/>
       <c r="L19" s="54"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="51"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
@@ -2719,15 +2694,15 @@
       <c r="K20" s="54"/>
       <c r="L20" s="54"/>
       <c r="R20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="54"/>
       <c r="E21" s="54" t="str">
@@ -2736,22 +2711,22 @@
       </c>
       <c r="F21" s="54"/>
       <c r="G21" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="57"/>
+      <c r="I21" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="H21" s="57"/>
-      <c r="I21" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="111"/>
+      <c r="J21" s="128"/>
       <c r="K21" s="66"/>
       <c r="L21" s="66"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="58" t="s">
         <v>43</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>44</v>
       </c>
       <c r="E22" s="54">
         <f>A5</f>
@@ -2765,21 +2740,21 @@
       <c r="K22" s="54"/>
       <c r="L22" s="54"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" s="51"/>
       <c r="D23" s="54"/>
       <c r="E23" s="54"/>
       <c r="F23" s="54"/>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="111"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="128"/>
       <c r="K23" s="66"/>
       <c r="L23" s="66"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" s="54"/>
       <c r="E24" s="54"/>
@@ -2787,16 +2762,16 @@
       <c r="G24" s="54"/>
       <c r="H24" s="63">
         <f>L$1/5</f>
-        <v>240000</v>
+        <v>188296.946</v>
       </c>
       <c r="I24" s="51"/>
       <c r="J24" s="52"/>
       <c r="K24" s="54"/>
       <c r="L24" s="54"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="54"/>
       <c r="E25" s="54"/>
@@ -2811,9 +2786,9 @@
       <c r="K25" s="54"/>
       <c r="L25" s="54"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="54"/>
       <c r="E26" s="54"/>
@@ -2828,9 +2803,9 @@
       <c r="K26" s="54"/>
       <c r="L26" s="54"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="54"/>
       <c r="E27" s="54"/>
@@ -2845,9 +2820,9 @@
       <c r="K27" s="54"/>
       <c r="L27" s="54"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="54"/>
       <c r="E28" s="54"/>
@@ -2862,7 +2837,7 @@
       <c r="K28" s="54"/>
       <c r="L28" s="54"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="D29" s="54"/>
       <c r="E29" s="54"/>
       <c r="F29" s="54"/>
@@ -2873,9 +2848,9 @@
       <c r="K29" s="54"/>
       <c r="L29" s="54"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="54"/>
       <c r="E30" s="54"/>
@@ -2890,7 +2865,7 @@
       <c r="K30" s="54"/>
       <c r="L30" s="54"/>
     </row>
-    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" s="51"/>
       <c r="D31" s="54"/>
       <c r="E31" s="54"/>
@@ -2902,71 +2877,71 @@
       <c r="K31" s="54"/>
       <c r="L31" s="54"/>
     </row>
-    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="96">
+    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="126"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="95">
         <f>SUM(H24:H31)</f>
-        <v>285366.38250000001</v>
+        <v>233663.3285</v>
       </c>
       <c r="I32" s="61"/>
       <c r="J32" s="62"/>
       <c r="K32" s="54"/>
       <c r="L32" s="54"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="108"/>
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C36" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
       <c r="I36" s="49"/>
       <c r="J36" s="50"/>
       <c r="K36" s="54"/>
       <c r="L36" s="54"/>
     </row>
-    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="108"/>
+    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="130"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="130"/>
+      <c r="H37" s="130"/>
       <c r="I37" s="51"/>
       <c r="J37" s="52"/>
       <c r="K37" s="54"/>
       <c r="L37" s="54"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" s="49"/>
       <c r="D38" s="53"/>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
       <c r="G38" s="54"/>
       <c r="H38" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I38" s="51"/>
       <c r="J38" s="52"/>
       <c r="K38" s="54"/>
       <c r="L38" s="54"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="54"/>
       <c r="E39" s="54"/>
@@ -2981,7 +2956,7 @@
       <c r="K39" s="54"/>
       <c r="L39" s="54"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" s="55"/>
       <c r="D40" s="56"/>
       <c r="E40" s="56"/>
@@ -2993,21 +2968,21 @@
       <c r="K40" s="54"/>
       <c r="L40" s="54"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="106"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="106"/>
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="132" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="133"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="133"/>
       <c r="I41" s="51"/>
       <c r="J41" s="52"/>
       <c r="K41" s="54"/>
       <c r="L41" s="54"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" s="51"/>
       <c r="D42" s="54"/>
       <c r="E42" s="54"/>
@@ -3019,9 +2994,9 @@
       <c r="K42" s="54"/>
       <c r="L42" s="54"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C43" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" s="54"/>
       <c r="E43" s="54" t="str">
@@ -3030,22 +3005,22 @@
       </c>
       <c r="F43" s="54"/>
       <c r="G43" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="57"/>
+      <c r="I43" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="H43" s="57"/>
-      <c r="I43" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="111"/>
+      <c r="J43" s="128"/>
       <c r="K43" s="66"/>
       <c r="L43" s="66"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="58" t="s">
         <v>43</v>
-      </c>
-      <c r="D44" s="58" t="s">
-        <v>44</v>
       </c>
       <c r="E44" s="54">
         <f>A7</f>
@@ -3059,21 +3034,21 @@
       <c r="K44" s="54"/>
       <c r="L44" s="54"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="51"/>
       <c r="D45" s="54"/>
       <c r="E45" s="54"/>
       <c r="F45" s="54"/>
       <c r="G45" s="54"/>
       <c r="H45" s="54"/>
-      <c r="I45" s="112"/>
-      <c r="J45" s="111"/>
+      <c r="I45" s="134"/>
+      <c r="J45" s="128"/>
       <c r="K45" s="66"/>
       <c r="L45" s="66"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" s="54"/>
       <c r="E46" s="54"/>
@@ -3081,14 +3056,14 @@
       <c r="G46" s="54"/>
       <c r="H46" s="63">
         <f>L$1/5</f>
-        <v>240000</v>
+        <v>188296.946</v>
       </c>
       <c r="I46" s="51"/>
       <c r="J46" s="52"/>
       <c r="K46" s="54"/>
       <c r="L46" s="54"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="51"/>
       <c r="D47" s="54"/>
       <c r="E47" s="54"/>
@@ -3100,7 +3075,7 @@
       <c r="K47" s="54"/>
       <c r="L47" s="54"/>
     </row>
-    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="51"/>
       <c r="D48" s="54"/>
       <c r="E48" s="54"/>
@@ -3112,15 +3087,15 @@
       <c r="K48" s="54"/>
       <c r="L48" s="54"/>
     </row>
-    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="114"/>
-      <c r="E49" s="114"/>
-      <c r="F49" s="114"/>
-      <c r="G49" s="114"/>
-      <c r="H49" s="96">
+    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
+      <c r="H49" s="95">
         <f>M6</f>
         <v>393669.3528471351</v>
       </c>
@@ -3129,53 +3104,53 @@
       <c r="K49" s="54"/>
       <c r="L49" s="54"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="108"/>
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C52" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="130"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="130"/>
+      <c r="H52" s="130"/>
       <c r="I52" s="49"/>
       <c r="J52" s="50"/>
       <c r="K52" s="54"/>
       <c r="L52" s="54"/>
     </row>
-    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="108"/>
-      <c r="H53" s="108"/>
+    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C53" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="130"/>
+      <c r="E53" s="130"/>
+      <c r="F53" s="130"/>
+      <c r="G53" s="130"/>
+      <c r="H53" s="130"/>
       <c r="I53" s="51"/>
       <c r="J53" s="52"/>
       <c r="K53" s="54"/>
       <c r="L53" s="54"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C54" s="49"/>
       <c r="D54" s="53"/>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
       <c r="G54" s="54"/>
       <c r="H54" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I54" s="51"/>
       <c r="J54" s="52"/>
       <c r="K54" s="54"/>
       <c r="L54" s="54"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C55" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D55" s="54"/>
       <c r="E55" s="54"/>
@@ -3190,7 +3165,7 @@
       <c r="K55" s="54"/>
       <c r="L55" s="54"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" s="55"/>
       <c r="D56" s="56"/>
       <c r="E56" s="56"/>
@@ -3202,21 +3177,21 @@
       <c r="K56" s="54"/>
       <c r="L56" s="54"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="132" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="133"/>
       <c r="I57" s="51"/>
       <c r="J57" s="52"/>
       <c r="K57" s="54"/>
       <c r="L57" s="54"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" s="51"/>
       <c r="D58" s="54"/>
       <c r="E58" s="54"/>
@@ -3228,9 +3203,9 @@
       <c r="K58" s="54"/>
       <c r="L58" s="54"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D59" s="54"/>
       <c r="E59" s="54" t="str">
@@ -3239,22 +3214,22 @@
       </c>
       <c r="F59" s="54"/>
       <c r="G59" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H59" s="57"/>
+      <c r="I59" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="H59" s="57"/>
-      <c r="I59" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J59" s="111"/>
+      <c r="J59" s="128"/>
       <c r="K59" s="66"/>
       <c r="L59" s="66"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="58" t="s">
         <v>43</v>
-      </c>
-      <c r="D60" s="58" t="s">
-        <v>44</v>
       </c>
       <c r="E60" s="54">
         <f>A6</f>
@@ -3268,21 +3243,21 @@
       <c r="K60" s="54"/>
       <c r="L60" s="54"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C61" s="51"/>
       <c r="D61" s="54"/>
       <c r="E61" s="54"/>
       <c r="F61" s="54"/>
       <c r="G61" s="54"/>
       <c r="H61" s="54"/>
-      <c r="I61" s="112"/>
-      <c r="J61" s="111"/>
+      <c r="I61" s="134"/>
+      <c r="J61" s="128"/>
       <c r="K61" s="66"/>
       <c r="L61" s="66"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C62" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D62" s="54"/>
       <c r="E62" s="54"/>
@@ -3290,16 +3265,16 @@
       <c r="G62" s="54"/>
       <c r="H62" s="63">
         <f>L$1/5</f>
-        <v>240000</v>
+        <v>188296.946</v>
       </c>
       <c r="I62" s="51"/>
       <c r="J62" s="52"/>
       <c r="K62" s="54"/>
       <c r="L62" s="54"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C63" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" s="54"/>
       <c r="E63" s="54"/>
@@ -3314,9 +3289,9 @@
       <c r="K63" s="54"/>
       <c r="L63" s="54"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C64" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D64" s="54"/>
       <c r="E64" s="54"/>
@@ -3331,9 +3306,9 @@
       <c r="K64" s="54"/>
       <c r="L64" s="54"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C65" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D65" s="54"/>
       <c r="E65" s="54"/>
@@ -3348,9 +3323,9 @@
       <c r="K65" s="54"/>
       <c r="L65" s="54"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C66" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" s="54"/>
       <c r="E66" s="54"/>
@@ -3365,7 +3340,7 @@
       <c r="K66" s="54"/>
       <c r="L66" s="54"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D67" s="54"/>
       <c r="E67" s="54"/>
       <c r="F67" s="54"/>
@@ -3376,9 +3351,9 @@
       <c r="K67" s="54"/>
       <c r="L67" s="54"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D68" s="54"/>
       <c r="E68" s="54"/>
@@ -3393,7 +3368,7 @@
       <c r="K68" s="54"/>
       <c r="L68" s="54"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="51"/>
       <c r="D69" s="54"/>
       <c r="E69" s="54"/>
@@ -3405,7 +3380,7 @@
       <c r="K69" s="54"/>
       <c r="L69" s="54"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C70" s="51"/>
       <c r="D70" s="54"/>
       <c r="E70" s="54"/>
@@ -3417,7 +3392,7 @@
       <c r="K70" s="54"/>
       <c r="L70" s="54"/>
     </row>
-    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C71" s="51"/>
       <c r="D71" s="54"/>
       <c r="E71" s="54"/>
@@ -3429,71 +3404,71 @@
       <c r="K71" s="54"/>
       <c r="L71" s="54"/>
     </row>
-    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="D72" s="114"/>
-      <c r="E72" s="114"/>
-      <c r="F72" s="114"/>
-      <c r="G72" s="114"/>
-      <c r="H72" s="96">
+    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C72" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="126"/>
+      <c r="E72" s="126"/>
+      <c r="F72" s="126"/>
+      <c r="G72" s="126"/>
+      <c r="H72" s="95">
         <f>SUM(H62:H71)</f>
-        <v>285366.38250000001</v>
+        <v>233663.3285</v>
       </c>
       <c r="I72" s="61"/>
       <c r="J72" s="62"/>
       <c r="K72" s="54"/>
       <c r="L72" s="54"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="108"/>
-      <c r="E76" s="108"/>
-      <c r="F76" s="108"/>
-      <c r="G76" s="108"/>
-      <c r="H76" s="108"/>
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C76" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" s="130"/>
+      <c r="E76" s="130"/>
+      <c r="F76" s="130"/>
+      <c r="G76" s="130"/>
+      <c r="H76" s="130"/>
       <c r="I76" s="49"/>
       <c r="J76" s="50"/>
       <c r="K76" s="54"/>
       <c r="L76" s="54"/>
     </row>
-    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="108"/>
-      <c r="E77" s="108"/>
-      <c r="F77" s="108"/>
-      <c r="G77" s="108"/>
-      <c r="H77" s="108"/>
+    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C77" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="130"/>
+      <c r="E77" s="130"/>
+      <c r="F77" s="130"/>
+      <c r="G77" s="130"/>
+      <c r="H77" s="130"/>
       <c r="I77" s="51"/>
       <c r="J77" s="52"/>
       <c r="K77" s="54"/>
       <c r="L77" s="54"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C78" s="49"/>
       <c r="D78" s="53"/>
       <c r="E78" s="53"/>
       <c r="F78" s="53"/>
       <c r="G78" s="54"/>
       <c r="H78" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I78" s="51"/>
       <c r="J78" s="52"/>
       <c r="K78" s="54"/>
       <c r="L78" s="54"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C79" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D79" s="54"/>
       <c r="E79" s="54"/>
@@ -3508,7 +3483,7 @@
       <c r="K79" s="54"/>
       <c r="L79" s="54"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C80" s="55"/>
       <c r="D80" s="56"/>
       <c r="E80" s="56"/>
@@ -3520,21 +3495,21 @@
       <c r="K80" s="54"/>
       <c r="L80" s="54"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="106"/>
-      <c r="H81" s="106"/>
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="132" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="133"/>
+      <c r="E81" s="133"/>
+      <c r="F81" s="133"/>
+      <c r="G81" s="133"/>
+      <c r="H81" s="133"/>
       <c r="I81" s="51"/>
       <c r="J81" s="52"/>
       <c r="K81" s="54"/>
       <c r="L81" s="54"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C82" s="51"/>
       <c r="D82" s="54"/>
       <c r="E82" s="54"/>
@@ -3546,9 +3521,9 @@
       <c r="K82" s="54"/>
       <c r="L82" s="54"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C83" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D83" s="54"/>
       <c r="E83" s="54" t="str">
@@ -3557,22 +3532,22 @@
       </c>
       <c r="F83" s="54"/>
       <c r="G83" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="57"/>
+      <c r="I83" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="H83" s="57"/>
-      <c r="I83" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" s="111"/>
+      <c r="J83" s="128"/>
       <c r="K83" s="66"/>
       <c r="L83" s="66"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C84" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="58" t="s">
         <v>43</v>
-      </c>
-      <c r="D84" s="58" t="s">
-        <v>44</v>
       </c>
       <c r="E84" s="54">
         <f>A8</f>
@@ -3586,21 +3561,21 @@
       <c r="K84" s="54"/>
       <c r="L84" s="54"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C85" s="51"/>
       <c r="D85" s="54"/>
       <c r="E85" s="54"/>
       <c r="F85" s="54"/>
       <c r="G85" s="54"/>
       <c r="H85" s="54"/>
-      <c r="I85" s="112"/>
-      <c r="J85" s="111"/>
+      <c r="I85" s="134"/>
+      <c r="J85" s="128"/>
       <c r="K85" s="66"/>
       <c r="L85" s="66"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C86" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D86" s="54"/>
       <c r="E86" s="54"/>
@@ -3608,16 +3583,16 @@
       <c r="G86" s="54"/>
       <c r="H86" s="63">
         <f>L$1/5</f>
-        <v>240000</v>
+        <v>188296.946</v>
       </c>
       <c r="I86" s="51"/>
       <c r="J86" s="52"/>
       <c r="K86" s="54"/>
       <c r="L86" s="54"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C87" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D87" s="54"/>
       <c r="E87" s="54"/>
@@ -3632,9 +3607,9 @@
       <c r="K87" s="54"/>
       <c r="L87" s="54"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C88" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D88" s="54"/>
       <c r="E88" s="54"/>
@@ -3649,9 +3624,9 @@
       <c r="K88" s="54"/>
       <c r="L88" s="54"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C89" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D89" s="54"/>
       <c r="E89" s="54"/>
@@ -3666,9 +3641,9 @@
       <c r="K89" s="54"/>
       <c r="L89" s="54"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D90" s="54"/>
       <c r="E90" s="54"/>
@@ -3683,7 +3658,7 @@
       <c r="K90" s="54"/>
       <c r="L90" s="54"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D91" s="54"/>
       <c r="E91" s="54"/>
       <c r="F91" s="54"/>
@@ -3694,9 +3669,9 @@
       <c r="K91" s="54"/>
       <c r="L91" s="54"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C92" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D92" s="54"/>
       <c r="E92" s="54"/>
@@ -3711,7 +3686,7 @@
       <c r="K92" s="54"/>
       <c r="L92" s="54"/>
     </row>
-    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="D93" s="54"/>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -3722,71 +3697,71 @@
       <c r="K93" s="54"/>
       <c r="L93" s="54"/>
     </row>
-    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="D94" s="114"/>
-      <c r="E94" s="114"/>
-      <c r="F94" s="114"/>
-      <c r="G94" s="114"/>
-      <c r="H94" s="96">
+    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C94" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="126"/>
+      <c r="E94" s="126"/>
+      <c r="F94" s="126"/>
+      <c r="G94" s="126"/>
+      <c r="H94" s="95">
         <f>SUM(H86:H93)</f>
-        <v>285366.38250000001</v>
+        <v>233663.3285</v>
       </c>
       <c r="I94" s="61"/>
       <c r="J94" s="62"/>
       <c r="K94" s="54"/>
       <c r="L94" s="54"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D98" s="108"/>
-      <c r="E98" s="108"/>
-      <c r="F98" s="108"/>
-      <c r="G98" s="108"/>
-      <c r="H98" s="108"/>
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C98" s="129" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="130"/>
+      <c r="E98" s="130"/>
+      <c r="F98" s="130"/>
+      <c r="G98" s="130"/>
+      <c r="H98" s="130"/>
       <c r="I98" s="49"/>
       <c r="J98" s="50"/>
       <c r="K98" s="54"/>
       <c r="L98" s="54"/>
     </row>
-    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="D99" s="108"/>
-      <c r="E99" s="108"/>
-      <c r="F99" s="108"/>
-      <c r="G99" s="108"/>
-      <c r="H99" s="108"/>
+    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C99" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99" s="130"/>
+      <c r="E99" s="130"/>
+      <c r="F99" s="130"/>
+      <c r="G99" s="130"/>
+      <c r="H99" s="130"/>
       <c r="I99" s="51"/>
       <c r="J99" s="52"/>
       <c r="K99" s="54"/>
       <c r="L99" s="54"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C100" s="49"/>
       <c r="D100" s="53"/>
       <c r="E100" s="53"/>
       <c r="F100" s="53"/>
       <c r="G100" s="54"/>
       <c r="H100" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I100" s="51"/>
       <c r="J100" s="52"/>
       <c r="K100" s="54"/>
       <c r="L100" s="54"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C101" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D101" s="54"/>
       <c r="E101" s="54"/>
@@ -3801,7 +3776,7 @@
       <c r="K101" s="54"/>
       <c r="L101" s="54"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C102" s="55"/>
       <c r="D102" s="56"/>
       <c r="E102" s="56"/>
@@ -3813,21 +3788,21 @@
       <c r="K102" s="54"/>
       <c r="L102" s="54"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D103" s="106"/>
-      <c r="E103" s="106"/>
-      <c r="F103" s="106"/>
-      <c r="G103" s="106"/>
-      <c r="H103" s="106"/>
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="132" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" s="133"/>
+      <c r="E103" s="133"/>
+      <c r="F103" s="133"/>
+      <c r="G103" s="133"/>
+      <c r="H103" s="133"/>
       <c r="I103" s="51"/>
       <c r="J103" s="52"/>
       <c r="K103" s="54"/>
       <c r="L103" s="54"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C104" s="51"/>
       <c r="D104" s="54"/>
       <c r="E104" s="54"/>
@@ -3839,9 +3814,9 @@
       <c r="K104" s="54"/>
       <c r="L104" s="54"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C105" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D105" s="54"/>
       <c r="E105" s="54" t="str">
@@ -3850,22 +3825,22 @@
       </c>
       <c r="F105" s="54"/>
       <c r="G105" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H105" s="57"/>
+      <c r="I105" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="H105" s="57"/>
-      <c r="I105" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="J105" s="111"/>
+      <c r="J105" s="128"/>
       <c r="K105" s="66"/>
       <c r="L105" s="66"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C106" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="D106" s="58" t="s">
         <v>43</v>
-      </c>
-      <c r="D106" s="58" t="s">
-        <v>44</v>
       </c>
       <c r="E106" s="54">
         <v>5</v>
@@ -3878,21 +3853,21 @@
       <c r="K106" s="54"/>
       <c r="L106" s="54"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C107" s="51"/>
       <c r="D107" s="54"/>
       <c r="E107" s="54"/>
       <c r="F107" s="54"/>
       <c r="G107" s="54"/>
       <c r="H107" s="54"/>
-      <c r="I107" s="112"/>
-      <c r="J107" s="111"/>
+      <c r="I107" s="134"/>
+      <c r="J107" s="128"/>
       <c r="K107" s="66"/>
       <c r="L107" s="66"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C108" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D108" s="54"/>
       <c r="E108" s="54"/>
@@ -3900,16 +3875,16 @@
       <c r="G108" s="54"/>
       <c r="H108" s="63">
         <f>L$1/5</f>
-        <v>240000</v>
+        <v>188296.946</v>
       </c>
       <c r="I108" s="51"/>
       <c r="J108" s="52"/>
       <c r="K108" s="54"/>
       <c r="L108" s="54"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C109" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109" s="54"/>
       <c r="E109" s="54"/>
@@ -3924,9 +3899,9 @@
       <c r="K109" s="54"/>
       <c r="L109" s="54"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C110" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D110" s="54"/>
       <c r="E110" s="54"/>
@@ -3941,9 +3916,9 @@
       <c r="K110" s="54"/>
       <c r="L110" s="54"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C111" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D111" s="54"/>
       <c r="E111" s="54"/>
@@ -3958,9 +3933,9 @@
       <c r="K111" s="54"/>
       <c r="L111" s="54"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="C112" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D112" s="54"/>
       <c r="E112" s="54"/>
@@ -3975,7 +3950,7 @@
       <c r="K112" s="54"/>
       <c r="L112" s="54"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D113" s="54"/>
       <c r="E113" s="54"/>
       <c r="F113" s="54"/>
@@ -3986,9 +3961,9 @@
       <c r="K113" s="54"/>
       <c r="L113" s="54"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C114" s="65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D114" s="54"/>
       <c r="E114" s="54"/>
@@ -4003,7 +3978,7 @@
       <c r="K114" s="54"/>
       <c r="L114" s="54"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D115" s="54"/>
       <c r="E115" s="54"/>
       <c r="F115" s="54"/>
@@ -4014,74 +3989,103 @@
       <c r="K115" s="54"/>
       <c r="L115" s="54"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="D116" s="114"/>
-      <c r="E116" s="114"/>
-      <c r="F116" s="114"/>
-      <c r="G116" s="114"/>
-      <c r="H116" s="96">
+    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C116" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D116" s="126"/>
+      <c r="E116" s="126"/>
+      <c r="F116" s="126"/>
+      <c r="G116" s="126"/>
+      <c r="H116" s="95">
         <f>SUM(H108:H115)</f>
-        <v>285366.38250000001</v>
+        <v>233663.3285</v>
       </c>
       <c r="I116" s="61"/>
       <c r="J116" s="62"/>
       <c r="K116" s="54"/>
       <c r="L116" s="54"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="123" t="s">
-        <v>64</v>
-      </c>
-      <c r="B119" s="124"/>
-      <c r="C119" s="124"/>
-      <c r="D119" s="124"/>
-      <c r="E119" s="124"/>
-      <c r="F119" s="124"/>
-      <c r="G119" s="124"/>
-      <c r="H119" s="124"/>
-      <c r="I119" s="124"/>
-      <c r="J119" s="124"/>
-      <c r="K119" s="124"/>
-      <c r="L119" s="124"/>
-      <c r="M119" s="125"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="126"/>
-      <c r="B120" s="127"/>
-      <c r="C120" s="127"/>
-      <c r="D120" s="127"/>
-      <c r="E120" s="127"/>
-      <c r="F120" s="127"/>
-      <c r="G120" s="127"/>
-      <c r="H120" s="127"/>
-      <c r="I120" s="127"/>
-      <c r="J120" s="127"/>
-      <c r="K120" s="127"/>
-      <c r="L120" s="127"/>
-      <c r="M120" s="128"/>
-    </row>
-    <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="129"/>
-      <c r="B121" s="130"/>
-      <c r="C121" s="130"/>
-      <c r="D121" s="130"/>
-      <c r="E121" s="130"/>
-      <c r="F121" s="130"/>
-      <c r="G121" s="130"/>
-      <c r="H121" s="130"/>
-      <c r="I121" s="130"/>
-      <c r="J121" s="130"/>
-      <c r="K121" s="130"/>
-      <c r="L121" s="130"/>
-      <c r="M121" s="131"/>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B119" s="113"/>
+      <c r="C119" s="113"/>
+      <c r="D119" s="113"/>
+      <c r="E119" s="113"/>
+      <c r="F119" s="113"/>
+      <c r="G119" s="113"/>
+      <c r="H119" s="113"/>
+      <c r="I119" s="113"/>
+      <c r="J119" s="113"/>
+      <c r="K119" s="113"/>
+      <c r="L119" s="113"/>
+      <c r="M119" s="114"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="115"/>
+      <c r="B120" s="116"/>
+      <c r="C120" s="116"/>
+      <c r="D120" s="116"/>
+      <c r="E120" s="116"/>
+      <c r="F120" s="116"/>
+      <c r="G120" s="116"/>
+      <c r="H120" s="116"/>
+      <c r="I120" s="116"/>
+      <c r="J120" s="116"/>
+      <c r="K120" s="116"/>
+      <c r="L120" s="116"/>
+      <c r="M120" s="117"/>
+    </row>
+    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="118"/>
+      <c r="B121" s="119"/>
+      <c r="C121" s="119"/>
+      <c r="D121" s="119"/>
+      <c r="E121" s="119"/>
+      <c r="F121" s="119"/>
+      <c r="G121" s="119"/>
+      <c r="H121" s="119"/>
+      <c r="I121" s="119"/>
+      <c r="J121" s="119"/>
+      <c r="K121" s="119"/>
+      <c r="L121" s="119"/>
+      <c r="M121" s="120"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="45">
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I45:J45"/>
     <mergeCell ref="A119:M121"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C4"/>
@@ -4098,34 +4102,6 @@
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="I107:J107"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
